--- a/src_files/data_files/hydropower-compilation.xlsx
+++ b/src_files/data_files/hydropower-compilation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BB\bb-dev\north_european_model\src_files\data_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9914B02-A5E4-443D-8FDE-ED08942C7B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3CA0553-41E4-4027-A7ED-07449862CE43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="747" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="133">
   <si>
     <t>AT00</t>
   </si>
@@ -266,12 +266,6 @@
     <t>LT00_rorTurbine</t>
   </si>
   <si>
-    <t>UC_AT00_reservoirTurbine</t>
-  </si>
-  <si>
-    <t>AT00_reservoirTurbine</t>
-  </si>
-  <si>
     <t>UC_ES00_reservoirTurbine</t>
   </si>
   <si>
@@ -312,15 +306,6 @@
   </si>
   <si>
     <t>SE03_reservoirTurbine</t>
-  </si>
-  <si>
-    <t>UC_SE04_reservoirTurbine</t>
-  </si>
-  <si>
-    <t>SE04_elec</t>
-  </si>
-  <si>
-    <t>SE04_reservoirTurbine</t>
   </si>
   <si>
     <t>penalty</t>
@@ -2699,7 +2684,7 @@
         <v>21</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F1" s="9" t="s">
         <v>25</v>
@@ -2720,28 +2705,28 @@
         <v>39</v>
       </c>
       <c r="O1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="P1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="Q1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="R1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="S1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="T1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="U1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="V1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
@@ -2802,7 +2787,7 @@
       <c r="J3" s="12"/>
       <c r="K3" s="12"/>
       <c r="P3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -2863,7 +2848,7 @@
       <c r="J5" s="12"/>
       <c r="K5" s="12"/>
       <c r="P5" s="38" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Q5" s="35"/>
       <c r="R5" s="35"/>
@@ -2905,7 +2890,7 @@
         <v>26406</v>
       </c>
       <c r="R6" s="35" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="S6" s="35"/>
       <c r="T6" s="35"/>
@@ -2945,7 +2930,7 @@
         <v>1007</v>
       </c>
       <c r="R7" s="35" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="S7" s="35"/>
       <c r="T7" s="35"/>
@@ -2985,7 +2970,7 @@
         <v>20748</v>
       </c>
       <c r="R8" s="35" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="S8" s="35"/>
       <c r="T8" s="35"/>
@@ -3025,7 +3010,7 @@
         <v>17189</v>
       </c>
       <c r="R9" s="35" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="S9" s="35"/>
       <c r="T9" s="35"/>
@@ -3065,7 +3050,7 @@
         <v>10316</v>
       </c>
       <c r="R10" s="35" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="S10" s="35"/>
       <c r="T10" s="35"/>
@@ -3105,7 +3090,7 @@
         <v>58717</v>
       </c>
       <c r="R11" s="35" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="S11" s="35"/>
       <c r="T11" s="35"/>
@@ -3145,7 +3130,7 @@
         <v>948</v>
       </c>
       <c r="R12" s="35" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="S12" s="35"/>
       <c r="T12" s="35"/>
@@ -3185,7 +3170,7 @@
         <v>7100</v>
       </c>
       <c r="R13" s="35" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="S13" s="35"/>
       <c r="T13" s="35"/>
@@ -3225,7 +3210,7 @@
         <v>1590</v>
       </c>
       <c r="R14" s="35" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="S14" s="35"/>
       <c r="T14" s="35"/>
@@ -4029,7 +4014,7 @@
         <v>19</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>20</v>
@@ -4041,22 +4026,22 @@
         <v>22</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K1" s="30" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>39</v>
@@ -4065,52 +4050,52 @@
         <v>37</v>
       </c>
       <c r="R1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="S1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="T1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="U1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="V1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="W1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="X1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="Y1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="Z1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="AA1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="AB1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="AC1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="AD1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="AE1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="AF1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="AG1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
@@ -4118,7 +4103,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
         <v>36</v>
@@ -4159,7 +4144,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C3" t="s">
         <v>36</v>
@@ -4195,7 +4180,7 @@
         <v>0.28699999999999998</v>
       </c>
       <c r="AA3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -4203,7 +4188,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
         <v>36</v>
@@ -4244,7 +4229,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
         <v>36</v>
@@ -4285,7 +4270,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
         <v>36</v>
@@ -4321,19 +4306,19 @@
         <v>0.75800000000000001</v>
       </c>
       <c r="U6" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="V6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="W6" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="X6" s="27" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="AA6" s="34" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
@@ -4341,7 +4326,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
         <v>36</v>
@@ -4396,16 +4381,16 @@
         <v>0.128</v>
       </c>
       <c r="AA7" s="37" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="AB7" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="AC7" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="AD7" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
@@ -4413,7 +4398,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
         <v>36</v>
@@ -4471,7 +4456,7 @@
         <v>0</v>
       </c>
       <c r="AB8" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AC8">
         <v>2.31E-3</v>
@@ -4485,7 +4470,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C9" t="s">
         <v>36</v>
@@ -4543,7 +4528,7 @@
         <v>0</v>
       </c>
       <c r="AB9" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="AC9">
         <v>5.0499999999999998E-3</v>
@@ -4557,7 +4542,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C10" t="s">
         <v>36</v>
@@ -4615,7 +4600,7 @@
         <v>0</v>
       </c>
       <c r="AB10" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="AC10">
         <v>7.7299999999999999E-3</v>
@@ -4629,7 +4614,7 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C11" t="s">
         <v>36</v>
@@ -4665,7 +4650,7 @@
         <v>0.82799999999999996</v>
       </c>
       <c r="T11" s="5" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U11" s="6">
         <f>'[1]vomcost mult'!O15</f>
@@ -4687,7 +4672,7 @@
         <v>1</v>
       </c>
       <c r="AB11" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AC11">
         <v>4.4000000000000003E-3</v>
@@ -4701,7 +4686,7 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C12" t="s">
         <v>36</v>
@@ -4737,7 +4722,7 @@
         <v/>
       </c>
       <c r="T12" s="5" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="U12" s="6">
         <f>'[1]vomcost mult'!O16</f>
@@ -4759,7 +4744,7 @@
         <v>1</v>
       </c>
       <c r="AB12" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="AC12">
         <v>1.3140000000000001E-2</v>
@@ -4773,7 +4758,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C13" t="s">
         <v>36</v>
@@ -4809,7 +4794,7 @@
         <v>0.69099999999999995</v>
       </c>
       <c r="T13" s="5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="U13" s="6">
         <f>'[1]vomcost mult'!O17</f>
@@ -4831,7 +4816,7 @@
         <v>2</v>
       </c>
       <c r="AB13" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AC13">
         <v>4.1599999999999996E-3</v>
@@ -4845,7 +4830,7 @@
         <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C14" t="s">
         <v>36</v>
@@ -4903,7 +4888,7 @@
         <v>2</v>
       </c>
       <c r="AB14" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="AC14">
         <v>5.7800000000000004E-3</v>
@@ -4917,7 +4902,7 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C15" t="s">
         <v>36</v>
@@ -4975,7 +4960,7 @@
         <v>2</v>
       </c>
       <c r="AB15" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="AC15">
         <v>5.6600000000000001E-3</v>
@@ -4989,7 +4974,7 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
         <v>36</v>
@@ -5047,7 +5032,7 @@
         <v>3</v>
       </c>
       <c r="AB16" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AC16">
         <v>2.9499999999999999E-3</v>
@@ -5061,7 +5046,7 @@
         <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
         <v>36</v>
@@ -5119,7 +5104,7 @@
         <v>3</v>
       </c>
       <c r="AB17" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="AC17">
         <v>6.0000000000000001E-3</v>
@@ -5133,7 +5118,7 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
         <v>36</v>
@@ -5191,7 +5176,7 @@
         <v>3</v>
       </c>
       <c r="AB18" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="AC18">
         <v>7.2399999999999999E-3</v>
@@ -5205,7 +5190,7 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C19" t="s">
         <v>36</v>
@@ -5263,7 +5248,7 @@
         <v>3</v>
       </c>
       <c r="AB19" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="AC19">
         <v>7.2399999999999999E-3</v>
@@ -5277,7 +5262,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
         <v>36</v>
@@ -5335,7 +5320,7 @@
         <v>4</v>
       </c>
       <c r="AB20" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AC20">
         <v>3.3700000000000002E-3</v>
@@ -5349,7 +5334,7 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C21" t="s">
         <v>36</v>
@@ -5407,7 +5392,7 @@
         <v>4</v>
       </c>
       <c r="AB21" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="AC21">
         <v>3.63E-3</v>
@@ -5421,7 +5406,7 @@
         <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C22" t="s">
         <v>36</v>
@@ -5479,7 +5464,7 @@
         <v>4</v>
       </c>
       <c r="AB22" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="AC22">
         <v>8.0999999999999996E-3</v>
@@ -5493,7 +5478,7 @@
         <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s">
         <v>36</v>
@@ -5551,7 +5536,7 @@
         <v>4</v>
       </c>
       <c r="AB23" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="AC23">
         <v>8.0999999999999996E-3</v>
@@ -5565,7 +5550,7 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C24" t="s">
         <v>36</v>
@@ -5623,7 +5608,7 @@
         <v>5</v>
       </c>
       <c r="AB24" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="AC24">
         <v>3.8500000000000001E-3</v>
@@ -5637,7 +5622,7 @@
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C25" t="s">
         <v>36</v>
@@ -5695,7 +5680,7 @@
         <v>6</v>
       </c>
       <c r="AB25" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AC25">
         <v>7.5500000000000003E-3</v>
@@ -5709,7 +5694,7 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C26" t="s">
         <v>36</v>
@@ -5767,7 +5752,7 @@
         <v>6</v>
       </c>
       <c r="AB26" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="AC26">
         <v>2.3700000000000001E-3</v>
@@ -5781,7 +5766,7 @@
         <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C27" t="s">
         <v>36</v>
@@ -5839,7 +5824,7 @@
         <v>6</v>
       </c>
       <c r="AB27" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="AC27">
         <v>9.3799999999999994E-3</v>
@@ -5853,7 +5838,7 @@
         <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C28" t="s">
         <v>36</v>
@@ -5911,7 +5896,7 @@
         <v>6</v>
       </c>
       <c r="AB28" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="AC28">
         <v>9.3799999999999994E-3</v>
@@ -5925,7 +5910,7 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C29" t="s">
         <v>36</v>
@@ -5964,7 +5949,7 @@
         <v>7</v>
       </c>
       <c r="AB29" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AC29">
         <v>9.4999999999999998E-3</v>
@@ -5978,7 +5963,7 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C30" t="s">
         <v>36</v>
@@ -6014,19 +5999,19 @@
         <v>0.92400000000000004</v>
       </c>
       <c r="U30" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="V30" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="W30" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="AA30" s="37" t="s">
         <v>7</v>
       </c>
       <c r="AB30" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="AC30">
         <v>1.268E-2</v>
@@ -6040,7 +6025,7 @@
         <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C31" t="s">
         <v>36</v>
@@ -6076,7 +6061,7 @@
         <v>0.95299999999999996</v>
       </c>
       <c r="T31" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="U31" s="8">
         <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$D:$D, $T31)</f>
@@ -6094,7 +6079,7 @@
         <v>8</v>
       </c>
       <c r="AB31" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AC31">
         <v>6.4700000000000001E-3</v>
@@ -6108,7 +6093,7 @@
         <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C32" t="s">
         <v>36</v>
@@ -6144,7 +6129,7 @@
         <v>0.90500000000000003</v>
       </c>
       <c r="T32" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="U32" s="8">
         <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$D:$D, $T32)</f>
@@ -6162,7 +6147,7 @@
         <v>10</v>
       </c>
       <c r="AB32" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="AC32">
         <v>5.0000000000000001E-3</v>
@@ -6176,7 +6161,7 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C33" t="s">
         <v>36</v>
@@ -6212,7 +6197,7 @@
         <v/>
       </c>
       <c r="T33" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="U33" s="8">
         <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$D:$D, $T33)</f>
@@ -6230,7 +6215,7 @@
         <v>11</v>
       </c>
       <c r="AB33" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="AC33">
         <v>6.5500000000000003E-3</v>
@@ -6244,7 +6229,7 @@
         <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C34" t="s">
         <v>36</v>
@@ -6280,7 +6265,7 @@
         <v>38</v>
       </c>
       <c r="T34" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="U34" s="8">
         <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$D:$D, $T34)</f>
@@ -6298,7 +6283,7 @@
         <v>12</v>
       </c>
       <c r="AB34" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="AC34">
         <v>4.4799999999999996E-3</v>
@@ -6312,7 +6297,7 @@
         <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C35" t="s">
         <v>36</v>
@@ -6348,7 +6333,7 @@
         <v/>
       </c>
       <c r="T35" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="U35" s="8">
         <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$D:$D, $T35)</f>
@@ -6366,7 +6351,7 @@
         <v>13</v>
       </c>
       <c r="AB35" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AC35">
         <v>3.7100000000000002E-3</v>
@@ -6380,7 +6365,7 @@
         <v>4</v>
       </c>
       <c r="B36" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C36" t="s">
         <v>36</v>
@@ -6416,7 +6401,7 @@
         <v/>
       </c>
       <c r="T36" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="U36" s="8">
         <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$D:$D, $T36)</f>
@@ -6434,7 +6419,7 @@
         <v>13</v>
       </c>
       <c r="AB36" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="AC36">
         <v>7.5399999999999998E-3</v>
@@ -6448,7 +6433,7 @@
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C37" t="s">
         <v>36</v>
@@ -6487,7 +6472,7 @@
         <v>13</v>
       </c>
       <c r="AB37" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="AC37">
         <v>1.108E-2</v>
@@ -6501,7 +6486,7 @@
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C38" t="s">
         <v>36</v>
@@ -6540,7 +6525,7 @@
         <v>13</v>
       </c>
       <c r="AB38" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="AC38">
         <v>1.108E-2</v>
@@ -6554,7 +6539,7 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C39" t="s">
         <v>36</v>
@@ -6593,13 +6578,13 @@
         <v>14</v>
       </c>
       <c r="AB39" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="AC39">
         <v>5.1399999999999996E-3</v>
       </c>
       <c r="AD39" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40" spans="1:30" x14ac:dyDescent="0.25">
@@ -6607,7 +6592,7 @@
         <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C40" t="s">
         <v>36</v>
@@ -6646,13 +6631,13 @@
         <v>15</v>
       </c>
       <c r="AB40" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="AC40">
         <v>5.5599999999999998E-3</v>
       </c>
       <c r="AD40" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="41" spans="1:30" x14ac:dyDescent="0.25">
@@ -6660,7 +6645,7 @@
         <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C41" t="s">
         <v>36</v>
@@ -6699,13 +6684,13 @@
         <v>16</v>
       </c>
       <c r="AB41" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="AC41">
         <v>6.4799999999999996E-3</v>
       </c>
       <c r="AD41" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="42" spans="1:30" x14ac:dyDescent="0.25">
@@ -6713,7 +6698,7 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C42" t="s">
         <v>36</v>
@@ -6752,13 +6737,13 @@
         <v>17</v>
       </c>
       <c r="AB42" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="AC42">
         <v>8.9899999999999997E-3</v>
       </c>
       <c r="AD42" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43" spans="1:30" x14ac:dyDescent="0.25">
@@ -6766,7 +6751,7 @@
         <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C43" t="s">
         <v>36</v>
@@ -6807,7 +6792,7 @@
         <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C44" t="s">
         <v>36</v>
@@ -6848,7 +6833,7 @@
         <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C45" t="s">
         <v>36</v>
@@ -6889,7 +6874,7 @@
         <v>4</v>
       </c>
       <c r="B46" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C46" t="s">
         <v>36</v>
@@ -6930,7 +6915,7 @@
         <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C47" t="s">
         <v>36</v>
@@ -6971,7 +6956,7 @@
         <v>7</v>
       </c>
       <c r="B48" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C48" t="s">
         <v>36</v>
@@ -7012,7 +6997,7 @@
         <v>13</v>
       </c>
       <c r="B49" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C49" t="s">
         <v>36</v>
@@ -7053,7 +7038,7 @@
         <v>18</v>
       </c>
       <c r="B50" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C50" t="s">
         <v>36</v>
@@ -7094,7 +7079,7 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C51" t="s">
         <v>36</v>
@@ -7135,7 +7120,7 @@
         <v>1</v>
       </c>
       <c r="B52" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C52" t="s">
         <v>36</v>
@@ -7176,7 +7161,7 @@
         <v>2</v>
       </c>
       <c r="B53" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C53" t="s">
         <v>36</v>
@@ -7217,7 +7202,7 @@
         <v>3</v>
       </c>
       <c r="B54" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C54" t="s">
         <v>36</v>
@@ -7258,7 +7243,7 @@
         <v>4</v>
       </c>
       <c r="B55" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C55" t="s">
         <v>36</v>
@@ -7299,7 +7284,7 @@
         <v>6</v>
       </c>
       <c r="B56" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C56" t="s">
         <v>36</v>
@@ -7340,7 +7325,7 @@
         <v>7</v>
       </c>
       <c r="B57" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C57" t="s">
         <v>36</v>
@@ -7381,7 +7366,7 @@
         <v>13</v>
       </c>
       <c r="B58" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C58" t="s">
         <v>36</v>
@@ -7422,7 +7407,7 @@
         <v>18</v>
       </c>
       <c r="B59" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C59" t="s">
         <v>36</v>
@@ -7468,7 +7453,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:S66"/>
+  <dimension ref="A1:S58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" style="6" bestFit="1" customWidth="1"/>
@@ -7513,25 +7498,25 @@
         <v>27</v>
       </c>
       <c r="M1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="N1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="O1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="P1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="Q1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="R1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="S1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
@@ -7630,7 +7615,7 @@
         <v>324</v>
       </c>
       <c r="N4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -7659,7 +7644,7 @@
         <v>34</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="J5" s="24">
         <v>300</v>
@@ -7787,7 +7772,7 @@
         <v>34</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="J9" s="24">
         <v>300</v>
@@ -7915,7 +7900,7 @@
         <v>34</v>
       </c>
       <c r="I13" s="23" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="J13" s="24">
         <v>300</v>
@@ -8043,7 +8028,7 @@
         <v>34</v>
       </c>
       <c r="I17" s="23" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="J17" s="24">
         <v>300</v>
@@ -8171,7 +8156,7 @@
         <v>34</v>
       </c>
       <c r="I21" s="23" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="J21" s="24">
         <v>300</v>
@@ -8299,7 +8284,7 @@
         <v>34</v>
       </c>
       <c r="I25" s="23" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="J25" s="24">
         <v>300</v>
@@ -8427,7 +8412,7 @@
         <v>34</v>
       </c>
       <c r="I29" s="23" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="J29" s="24">
         <v>300</v>
@@ -8529,7 +8514,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="26" t="s">
         <v>36</v>
       </c>
@@ -8555,13 +8540,13 @@
         <v>34</v>
       </c>
       <c r="I33" s="23" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="J33" s="24">
         <v>300</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="26" t="s">
         <v>36</v>
       </c>
@@ -8569,7 +8554,7 @@
         <v>1</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D34" s="22" t="s">
         <v>74</v>
@@ -8578,7 +8563,7 @@
         <v>48</v>
       </c>
       <c r="F34" s="22" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G34" s="22" t="s">
         <v>75</v>
@@ -8593,7 +8578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
         <v>36</v>
       </c>
@@ -8601,7 +8586,7 @@
         <v>1</v>
       </c>
       <c r="C35" s="26" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D35" s="22" t="s">
         <v>74</v>
@@ -8625,7 +8610,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="26" t="s">
         <v>36</v>
       </c>
@@ -8633,7 +8618,7 @@
         <v>1</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D36" s="22" t="s">
         <v>74</v>
@@ -8654,11 +8639,10 @@
         <v>28</v>
       </c>
       <c r="J36" s="24">
-        <v>7</v>
-      </c>
-      <c r="N36" s="34"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="26" t="s">
         <v>36</v>
       </c>
@@ -8666,7 +8650,7 @@
         <v>1</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D37" s="22" t="s">
         <v>74</v>
@@ -8684,13 +8668,13 @@
         <v>34</v>
       </c>
       <c r="I37" s="23" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="J37" s="24">
         <v>300</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="26" t="s">
         <v>36</v>
       </c>
@@ -8698,7 +8682,7 @@
         <v>1</v>
       </c>
       <c r="C38" s="26" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D38" s="22" t="s">
         <v>76</v>
@@ -8707,10 +8691,10 @@
         <v>48</v>
       </c>
       <c r="F38" s="22" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="G38" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H38" s="22" t="s">
         <v>34</v>
@@ -8722,7 +8706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
         <v>36</v>
       </c>
@@ -8730,7 +8714,7 @@
         <v>1</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D39" s="22" t="s">
         <v>76</v>
@@ -8754,7 +8738,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="26" t="s">
         <v>36</v>
       </c>
@@ -8762,7 +8746,7 @@
         <v>1</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D40" s="22" t="s">
         <v>76</v>
@@ -8783,10 +8767,10 @@
         <v>28</v>
       </c>
       <c r="J40" s="24">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
         <v>36</v>
       </c>
@@ -8794,7 +8778,7 @@
         <v>1</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D41" s="22" t="s">
         <v>76</v>
@@ -8812,13 +8796,13 @@
         <v>34</v>
       </c>
       <c r="I41" s="23" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="J41" s="24">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="26" t="s">
         <v>36</v>
       </c>
@@ -8826,19 +8810,19 @@
         <v>1</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D42" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E42" s="23" t="s">
         <v>48</v>
       </c>
       <c r="F42" s="22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G42" s="22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H42" s="22" t="s">
         <v>34</v>
@@ -8850,7 +8834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
         <v>36</v>
       </c>
@@ -8858,10 +8842,10 @@
         <v>1</v>
       </c>
       <c r="C43" s="26" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D43" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E43" s="23" t="s">
         <v>34</v>
@@ -8882,7 +8866,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="26" t="s">
         <v>36</v>
       </c>
@@ -8890,10 +8874,10 @@
         <v>1</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D44" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E44" s="23" t="s">
         <v>34</v>
@@ -8911,10 +8895,10 @@
         <v>28</v>
       </c>
       <c r="J44" s="24">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="26" t="s">
         <v>36</v>
       </c>
@@ -8922,10 +8906,10 @@
         <v>1</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D45" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E45" s="23" t="s">
         <v>34</v>
@@ -8940,13 +8924,13 @@
         <v>34</v>
       </c>
       <c r="I45" s="23" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="J45" s="24">
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="26" t="s">
         <v>36</v>
       </c>
@@ -8954,19 +8938,19 @@
         <v>1</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D46" s="22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E46" s="23" t="s">
         <v>48</v>
       </c>
       <c r="F46" s="22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G46" s="22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H46" s="22" t="s">
         <v>34</v>
@@ -8978,7 +8962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="26" t="s">
         <v>36</v>
       </c>
@@ -8986,10 +8970,10 @@
         <v>1</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D47" s="22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E47" s="23" t="s">
         <v>34</v>
@@ -9010,7 +8994,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="26" t="s">
         <v>36</v>
       </c>
@@ -9018,10 +9002,10 @@
         <v>1</v>
       </c>
       <c r="C48" s="26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D48" s="22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E48" s="23" t="s">
         <v>34</v>
@@ -9039,7 +9023,7 @@
         <v>28</v>
       </c>
       <c r="J48" s="24">
-        <v>250</v>
+        <v>824</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -9050,10 +9034,10 @@
         <v>1</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D49" s="22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E49" s="23" t="s">
         <v>34</v>
@@ -9068,7 +9052,7 @@
         <v>34</v>
       </c>
       <c r="I49" s="23" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="J49" s="24">
         <v>300</v>
@@ -9082,19 +9066,19 @@
         <v>1</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D50" s="22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E50" s="23" t="s">
         <v>48</v>
       </c>
       <c r="F50" s="22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G50" s="22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H50" s="22" t="s">
         <v>34</v>
@@ -9114,10 +9098,10 @@
         <v>1</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D51" s="22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E51" s="23" t="s">
         <v>34</v>
@@ -9146,10 +9130,10 @@
         <v>1</v>
       </c>
       <c r="C52" s="26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D52" s="22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E52" s="23" t="s">
         <v>34</v>
@@ -9167,7 +9151,7 @@
         <v>28</v>
       </c>
       <c r="J52" s="24">
-        <v>824</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -9178,10 +9162,10 @@
         <v>1</v>
       </c>
       <c r="C53" s="26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D53" s="22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E53" s="23" t="s">
         <v>34</v>
@@ -9196,327 +9180,71 @@
         <v>34</v>
       </c>
       <c r="I53" s="23" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="J53" s="24">
         <v>300</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B54" s="26">
-        <v>1</v>
-      </c>
-      <c r="C54" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="D54" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="E54" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="F54" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="G54" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="H54" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I54" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="J54" s="24">
-        <v>1</v>
-      </c>
+      <c r="A54" s="26"/>
+      <c r="B54" s="26"/>
+      <c r="C54" s="26"/>
+      <c r="D54" s="22"/>
+      <c r="E54" s="23"/>
+      <c r="F54" s="22"/>
+      <c r="G54" s="22"/>
+      <c r="H54" s="22"/>
+      <c r="I54" s="23"/>
+      <c r="J54" s="24"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B55" s="26">
-        <v>1</v>
-      </c>
-      <c r="C55" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="D55" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="E55" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F55" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G55" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H55" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I55" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="J55" s="24">
-        <v>-1</v>
-      </c>
+      <c r="A55" s="26"/>
+      <c r="B55" s="26"/>
+      <c r="C55" s="26"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="23"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="22"/>
+      <c r="H55" s="22"/>
+      <c r="I55" s="23"/>
+      <c r="J55" s="24"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B56" s="26">
-        <v>1</v>
-      </c>
-      <c r="C56" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="D56" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="E56" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F56" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G56" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H56" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I56" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="J56" s="24">
-        <v>108</v>
-      </c>
+      <c r="A56" s="26"/>
+      <c r="B56" s="26"/>
+      <c r="C56" s="26"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="22"/>
+      <c r="G56" s="22"/>
+      <c r="H56" s="22"/>
+      <c r="I56" s="23"/>
+      <c r="J56" s="24"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B57" s="26">
-        <v>1</v>
-      </c>
-      <c r="C57" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="D57" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="E57" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F57" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G57" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H57" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I57" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="J57" s="24">
-        <v>300</v>
-      </c>
+      <c r="A57" s="26"/>
+      <c r="B57" s="26"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="23"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="22"/>
+      <c r="H57" s="22"/>
+      <c r="I57" s="23"/>
+      <c r="J57" s="24"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B58" s="26">
-        <v>1</v>
-      </c>
-      <c r="C58" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="D58" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="E58" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="F58" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="G58" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="H58" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I58" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="J58" s="24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B59" s="26">
-        <v>1</v>
-      </c>
-      <c r="C59" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="D59" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="E59" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F59" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G59" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H59" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I59" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="J59" s="24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B60" s="26">
-        <v>1</v>
-      </c>
-      <c r="C60" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="D60" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="E60" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F60" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G60" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H60" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I60" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="J60" s="24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B61" s="26">
-        <v>1</v>
-      </c>
-      <c r="C61" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="D61" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="E61" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F61" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G61" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H61" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I61" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="J61" s="24">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="26"/>
-      <c r="B62" s="26"/>
-      <c r="C62" s="26"/>
-      <c r="D62" s="22"/>
-      <c r="E62" s="23"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="22"/>
-      <c r="H62" s="22"/>
-      <c r="I62" s="23"/>
-      <c r="J62" s="24"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="26"/>
-      <c r="B63" s="26"/>
-      <c r="C63" s="26"/>
-      <c r="D63" s="22"/>
-      <c r="E63" s="23"/>
-      <c r="F63" s="22"/>
-      <c r="G63" s="22"/>
-      <c r="H63" s="22"/>
-      <c r="I63" s="23"/>
-      <c r="J63" s="24"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="26"/>
-      <c r="B64" s="26"/>
-      <c r="C64" s="26"/>
-      <c r="D64" s="22"/>
-      <c r="E64" s="23"/>
-      <c r="F64" s="22"/>
-      <c r="G64" s="22"/>
-      <c r="H64" s="22"/>
-      <c r="I64" s="23"/>
-      <c r="J64" s="24"/>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="26"/>
-      <c r="B65" s="26"/>
-      <c r="C65" s="26"/>
-      <c r="D65" s="22"/>
-      <c r="E65" s="23"/>
-      <c r="F65" s="22"/>
-      <c r="G65" s="22"/>
-      <c r="H65" s="22"/>
-      <c r="I65" s="23"/>
-      <c r="J65" s="24"/>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="26"/>
-      <c r="B66" s="26"/>
-      <c r="C66" s="26"/>
-      <c r="D66" s="22"/>
-      <c r="E66" s="23"/>
-      <c r="F66" s="22"/>
-      <c r="G66" s="22"/>
-      <c r="H66" s="22"/>
-      <c r="I66" s="23"/>
-      <c r="J66" s="24"/>
+      <c r="A58" s="26"/>
+      <c r="B58" s="26"/>
+      <c r="C58" s="26"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="23"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="22"/>
+      <c r="I58" s="23"/>
+      <c r="J58" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src_files/data_files/hydropower-compilation.xlsx
+++ b/src_files/data_files/hydropower-compilation.xlsx
@@ -8,18 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BB\bb-dev\north_european_model\src_files\data_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3CA0553-41E4-4027-A7ED-07449862CE43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E8FC15-7493-4D49-B15B-252B3F97727A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="747" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="1080" windowWidth="21600" windowHeight="12585" tabRatio="747" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nodedata" sheetId="13" r:id="rId1"/>
     <sheet name="unitdata" sheetId="14" r:id="rId2"/>
-    <sheet name="userconstraintdata" sheetId="17" r:id="rId3"/>
   </sheets>
   <externalReferences>
+    <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
-    <externalReference r:id="rId5"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="82">
   <si>
     <t>AT00</t>
   </si>
@@ -113,9 +112,6 @@
     <t>capacity_output1</t>
   </si>
   <si>
-    <t>year</t>
-  </si>
-  <si>
     <t>reservoir</t>
   </si>
   <si>
@@ -125,12 +121,6 @@
     <t>psOpen</t>
   </si>
   <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>constant</t>
-  </si>
-  <si>
     <t>psClosed</t>
   </si>
   <si>
@@ -146,9 +136,6 @@
     <t>ror</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>Grid</t>
   </si>
   <si>
@@ -162,153 +149,6 @@
   </si>
   <si>
     <t>Note</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>1st dimension</t>
-  </si>
-  <si>
-    <t>2nd dimension</t>
-  </si>
-  <si>
-    <t>3rd dimension</t>
-  </si>
-  <si>
-    <t>4th dimension</t>
-  </si>
-  <si>
-    <t>parameter</t>
-  </si>
-  <si>
-    <t>country</t>
-  </si>
-  <si>
-    <t>UC_NOM1_psOpenTurbine</t>
-  </si>
-  <si>
-    <t>elec</t>
-  </si>
-  <si>
-    <t>NOM1_elec</t>
-  </si>
-  <si>
-    <t>NOM1_psOpenTurbine</t>
-  </si>
-  <si>
-    <t>v_gen</t>
-  </si>
-  <si>
-    <t>gt</t>
-  </si>
-  <si>
-    <t>UC_NON1_psOpenTurbine</t>
-  </si>
-  <si>
-    <t>NON1_elec</t>
-  </si>
-  <si>
-    <t>NON1_psOpenTurbine</t>
-  </si>
-  <si>
-    <t>UC_NOS0_psOpenTurbine</t>
-  </si>
-  <si>
-    <t>NOS0_elec</t>
-  </si>
-  <si>
-    <t>NOS0_psOpenTurbine</t>
-  </si>
-  <si>
-    <t>UC_AT00_rorTurbine</t>
-  </si>
-  <si>
-    <t>AT00_elec</t>
-  </si>
-  <si>
-    <t>AT00_rorTurbine</t>
-  </si>
-  <si>
-    <t>UC_DE00_rorTurbine</t>
-  </si>
-  <si>
-    <t>DE00_elec</t>
-  </si>
-  <si>
-    <t>DE00_rorTurbine</t>
-  </si>
-  <si>
-    <t>UC_ES00_rorTurbine</t>
-  </si>
-  <si>
-    <t>ES00_elec</t>
-  </si>
-  <si>
-    <t>ES00_rorTurbine</t>
-  </si>
-  <si>
-    <t>UC_FR00_rorTurbine</t>
-  </si>
-  <si>
-    <t>FR00_elec</t>
-  </si>
-  <si>
-    <t>FR00_rorTurbine</t>
-  </si>
-  <si>
-    <t>UC_LT00_rorTurbine</t>
-  </si>
-  <si>
-    <t>LT00_elec</t>
-  </si>
-  <si>
-    <t>LT00_rorTurbine</t>
-  </si>
-  <si>
-    <t>UC_ES00_reservoirTurbine</t>
-  </si>
-  <si>
-    <t>ES00_reservoirTurbine</t>
-  </si>
-  <si>
-    <t>UC_FI00_reservoirTurbine</t>
-  </si>
-  <si>
-    <t>FI00_elec</t>
-  </si>
-  <si>
-    <t>FI00_reservoirTurbine</t>
-  </si>
-  <si>
-    <t>UC_SE01_reservoirTurbine</t>
-  </si>
-  <si>
-    <t>SE01_elec</t>
-  </si>
-  <si>
-    <t>SE01_reservoirTurbine</t>
-  </si>
-  <si>
-    <t>UC_SE02_reservoirTurbine</t>
-  </si>
-  <si>
-    <t>SE02_elec</t>
-  </si>
-  <si>
-    <t>SE02_reservoirTurbine</t>
-  </si>
-  <si>
-    <t>UC_SE03_reservoirTurbine</t>
-  </si>
-  <si>
-    <t>SE03_elec</t>
-  </si>
-  <si>
-    <t>SE03_reservoirTurbine</t>
-  </si>
-  <si>
-    <t>penalty</t>
   </si>
   <si>
     <t>nodeBalance</t>
@@ -522,7 +362,13 @@
     <t>—</t>
   </si>
   <si>
-    <t>Minimum generations adapted from Kiehle et al 2026</t>
+    <t>minGen</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>minGenPenalty</t>
   </si>
 </sst>
 </file>
@@ -533,7 +379,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -573,22 +419,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -653,7 +483,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -692,24 +522,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC5E0B3"/>
-        <bgColor rgb="FFC5E0B3"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -752,29 +576,14 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="9" tint="0.59996337778862885"/>
-      </left>
-      <right style="thin">
-        <color theme="9" tint="0.59996337778862885"/>
-      </right>
-      <top style="thin">
-        <color theme="9" tint="0.59996337778862885"/>
-      </top>
-      <bottom style="thin">
-        <color theme="9" tint="0.59996337778862885"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -811,23 +620,7 @@
     <xf numFmtId="3" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -843,27 +636,30 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2675,7 +2471,7 @@
         <v>19</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>20</v>
@@ -2684,49 +2480,49 @@
         <v>21</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="K1" s="31" t="s">
-        <v>39</v>
+        <v>33</v>
+      </c>
+      <c r="K1" s="23" t="s">
+        <v>35</v>
       </c>
       <c r="O1" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="P1" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="Q1" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="R1" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="S1" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="T1" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="U1" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="V1" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
@@ -2734,10 +2530,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D2" s="6">
         <v>1</v>
@@ -2763,10 +2559,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D3" s="6">
         <v>1</v>
@@ -2787,7 +2583,7 @@
       <c r="J3" s="12"/>
       <c r="K3" s="12"/>
       <c r="P3" t="s">
-        <v>115</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -2795,10 +2591,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D4" s="6">
         <v>1</v>
@@ -2824,10 +2620,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D5" s="6">
         <v>1</v>
@@ -2847,23 +2643,23 @@
       </c>
       <c r="J5" s="12"/>
       <c r="K5" s="12"/>
-      <c r="P5" s="38" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q5" s="35"/>
-      <c r="R5" s="35"/>
-      <c r="S5" s="35"/>
-      <c r="T5" s="35"/>
+      <c r="P5" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q5" s="27"/>
+      <c r="R5" s="27"/>
+      <c r="S5" s="27"/>
+      <c r="T5" s="27"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D6" s="6">
         <v>1</v>
@@ -2883,27 +2679,27 @@
       </c>
       <c r="J6" s="12"/>
       <c r="K6" s="12"/>
-      <c r="P6" s="36" t="s">
+      <c r="P6" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="Q6" s="35">
+      <c r="Q6" s="27">
         <v>26406</v>
       </c>
-      <c r="R6" s="35" t="s">
-        <v>116</v>
-      </c>
-      <c r="S6" s="35"/>
-      <c r="T6" s="35"/>
+      <c r="R6" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="S6" s="27"/>
+      <c r="T6" s="27"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D7" s="6">
         <v>1</v>
@@ -2923,27 +2719,27 @@
       </c>
       <c r="J7" s="12"/>
       <c r="K7" s="12"/>
-      <c r="P7" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="35">
+      <c r="P7" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="27">
         <v>1007</v>
       </c>
-      <c r="R7" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="S7" s="35"/>
-      <c r="T7" s="35"/>
+      <c r="R7" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="S7" s="27"/>
+      <c r="T7" s="27"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D8" s="6">
         <v>1</v>
@@ -2963,27 +2759,27 @@
       </c>
       <c r="J8" s="12"/>
       <c r="K8" s="12"/>
-      <c r="P8" s="36" t="s">
+      <c r="P8" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="Q8" s="35">
+      <c r="Q8" s="27">
         <v>20748</v>
       </c>
-      <c r="R8" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="S8" s="35"/>
-      <c r="T8" s="35"/>
+      <c r="R8" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="S8" s="27"/>
+      <c r="T8" s="27"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D9" s="6">
         <v>1</v>
@@ -3003,27 +2799,27 @@
       </c>
       <c r="J9" s="12"/>
       <c r="K9" s="12"/>
-      <c r="P9" s="36" t="s">
+      <c r="P9" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="35">
+      <c r="Q9" s="27">
         <v>17189</v>
       </c>
-      <c r="R9" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="S9" s="35"/>
-      <c r="T9" s="35"/>
+      <c r="R9" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="S9" s="27"/>
+      <c r="T9" s="27"/>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D10" s="6">
         <v>1</v>
@@ -3043,27 +2839,27 @@
       </c>
       <c r="J10" s="12"/>
       <c r="K10" s="12"/>
-      <c r="P10" s="36" t="s">
+      <c r="P10" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="Q10" s="35">
+      <c r="Q10" s="27">
         <v>10316</v>
       </c>
-      <c r="R10" s="35" t="s">
-        <v>120</v>
-      </c>
-      <c r="S10" s="35"/>
-      <c r="T10" s="35"/>
+      <c r="R10" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="S10" s="27"/>
+      <c r="T10" s="27"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D11" s="6">
         <v>1</v>
@@ -3083,27 +2879,27 @@
       </c>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
-      <c r="P11" s="36" t="s">
+      <c r="P11" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="Q11" s="35">
+      <c r="Q11" s="27">
         <v>58717</v>
       </c>
-      <c r="R11" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="S11" s="35"/>
-      <c r="T11" s="35"/>
+      <c r="R11" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="S11" s="27"/>
+      <c r="T11" s="27"/>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D12" s="6">
         <v>1</v>
@@ -3123,27 +2919,27 @@
       </c>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
-      <c r="P12" s="36" t="s">
+      <c r="P12" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="Q12" s="35">
+      <c r="Q12" s="27">
         <v>948</v>
       </c>
-      <c r="R12" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="S12" s="35"/>
-      <c r="T12" s="35"/>
+      <c r="R12" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="S12" s="27"/>
+      <c r="T12" s="27"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D13" s="6">
         <v>1</v>
@@ -3163,27 +2959,27 @@
       </c>
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
-      <c r="P13" s="36" t="s">
+      <c r="P13" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="Q13" s="35">
+      <c r="Q13" s="27">
         <v>7100</v>
       </c>
-      <c r="R13" s="35" t="s">
-        <v>123</v>
-      </c>
-      <c r="S13" s="35"/>
-      <c r="T13" s="35"/>
+      <c r="R13" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="S13" s="27"/>
+      <c r="T13" s="27"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D14" s="6">
         <v>1</v>
@@ -3203,27 +2999,27 @@
       </c>
       <c r="J14" s="12"/>
       <c r="K14" s="12"/>
-      <c r="P14" s="36" t="s">
+      <c r="P14" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="Q14" s="35">
+      <c r="Q14" s="27">
         <v>1590</v>
       </c>
-      <c r="R14" s="35" t="s">
-        <v>124</v>
-      </c>
-      <c r="S14" s="35"/>
-      <c r="T14" s="35"/>
+      <c r="R14" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="S14" s="27"/>
+      <c r="T14" s="27"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D15" s="6">
         <v>1</v>
@@ -3249,10 +3045,10 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D16" s="6">
         <v>1</v>
@@ -3278,10 +3074,10 @@
         <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D17" s="6">
         <v>1</v>
@@ -3307,10 +3103,10 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D18" s="6">
         <v>1</v>
@@ -3336,10 +3132,10 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D19" s="6">
         <v>1</v>
@@ -3365,10 +3161,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D20" s="6">
         <v>1</v>
@@ -3394,10 +3190,10 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D21" s="6">
         <v>1</v>
@@ -3416,17 +3212,17 @@
         <v>40000</v>
       </c>
       <c r="J21" s="12"/>
-      <c r="K21" s="32"/>
+      <c r="K21" s="24"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D22" s="6">
         <v>1</v>
@@ -3452,10 +3248,10 @@
         <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D23" s="6">
         <v>1</v>
@@ -3481,10 +3277,10 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D24" s="6">
         <v>1</v>
@@ -3510,10 +3306,10 @@
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D25" s="6">
         <v>1</v>
@@ -3525,7 +3321,7 @@
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
       <c r="J25" s="12" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="K25" s="12"/>
     </row>
@@ -3534,10 +3330,10 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D26" s="6">
         <v>1</v>
@@ -3563,10 +3359,10 @@
         <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D27" s="6">
         <v>1</v>
@@ -3592,10 +3388,10 @@
         <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D28" s="6">
         <v>1</v>
@@ -3621,10 +3417,10 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D29" s="6">
         <v>1</v>
@@ -3650,10 +3446,10 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D30" s="6">
         <v>1</v>
@@ -3672,17 +3468,17 @@
         <v>40000</v>
       </c>
       <c r="J30" s="12"/>
-      <c r="K30" s="32"/>
+      <c r="K30" s="24"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
         <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D31" s="6">
         <v>1</v>
@@ -3701,17 +3497,17 @@
         <v>80000</v>
       </c>
       <c r="J31" s="12"/>
-      <c r="K31" s="32"/>
+      <c r="K31" s="24"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
         <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D32" s="6">
         <v>1</v>
@@ -3737,10 +3533,10 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D33" s="6">
         <v>1</v>
@@ -3752,7 +3548,7 @@
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
       <c r="J33" s="12" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="K33" s="12"/>
     </row>
@@ -3761,10 +3557,10 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D34" s="6">
         <v>1</v>
@@ -3788,10 +3584,10 @@
         <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D35" s="6">
         <v>1</v>
@@ -3815,10 +3611,10 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D36" s="6">
         <v>1</v>
@@ -3842,10 +3638,10 @@
         <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D37" s="6">
         <v>1</v>
@@ -3869,10 +3665,10 @@
         <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D38" s="6">
         <v>1</v>
@@ -3896,10 +3692,10 @@
         <v>7</v>
       </c>
       <c r="B39" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D39" s="6">
         <v>1</v>
@@ -3923,10 +3719,10 @@
         <v>13</v>
       </c>
       <c r="B40" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D40" s="6">
         <v>1</v>
@@ -3950,10 +3746,10 @@
         <v>18</v>
       </c>
       <c r="B41" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D41" s="6">
         <v>1</v>
@@ -3973,7 +3769,7 @@
       <c r="K41" s="12"/>
     </row>
     <row r="70" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P70" s="33"/>
+      <c r="P70" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3988,7 +3784,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:AG59"/>
+  <dimension ref="A1:AH59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -3999,22 +3795,25 @@
     <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="14.7109375" customWidth="1"/>
-    <col min="12" max="12" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="0" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="21" hidden="1" customWidth="1"/>
-    <col min="18" max="19" width="0" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="20.85546875" hidden="1" customWidth="1"/>
-    <col min="21" max="24" width="0" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="13.140625" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" customWidth="1"/>
+    <col min="11" max="11" width="8.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" customWidth="1"/>
+    <col min="14" max="14" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.140625" customWidth="1"/>
+    <col min="19" max="19" width="20.85546875" customWidth="1"/>
+    <col min="20" max="25" width="9.140625" customWidth="1"/>
+    <col min="26" max="26" width="13.140625" customWidth="1"/>
+    <col min="30" max="30" width="9.85546875" customWidth="1"/>
+    <col min="31" max="31" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>20</v>
@@ -4025,88 +3824,97 @@
       <c r="E1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="G1" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="H1" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="I1" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="J1" s="30" t="s">
-        <v>113</v>
-      </c>
-      <c r="K1" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="M1" s="5" t="s">
+      <c r="F1" s="22" t="s">
         <v>37</v>
       </c>
+      <c r="G1" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="L1" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="M1" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>33</v>
+      </c>
       <c r="R1" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="S1" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="T1" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="U1" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="V1" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="W1" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="X1" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="Y1" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="Z1" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="AA1" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="AB1" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="AC1" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="AD1" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="AE1" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="AF1" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="AG1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -4115,39 +3923,47 @@
         <v>5782</v>
       </c>
       <c r="F2">
-        <f>ROUND(SUMIFS(U$31:U$36,$T$31:$T$36,$B2) * (1 + SUMIFS($X$7:$X$28,$T$7:$T$28,$A2)), 2)</f>
+        <f t="shared" ref="F2:F33" si="0">ROUND(SUMIFS(T$31:T$36,$S$31:$S$36,$B2) * (1 + SUMIFS($W$7:$W$28,$S$7:$S$28,$A2)), 2)</f>
         <v>2.2599999999999998</v>
       </c>
       <c r="G2">
-        <f t="shared" ref="G2:G59" si="0">ROUND(SUMIFS(V$31:V$36,$T$31:$T$36,$B2) * (1 + SUMIFS($X$7:$X$28,$T$7:$T$28,$A2)), 2)</f>
+        <f t="shared" ref="G2:G33" si="1">ROUND(SUMIFS(U$31:U$36,$S$31:$S$36,$B2) * (1 + SUMIFS($W$7:$W$28,$S$7:$S$28,$A2)), 2)</f>
         <v>6.2</v>
       </c>
       <c r="H2">
-        <f t="shared" ref="H2:H59" si="1">ROUND(SUMIFS(W$31:W$36,$T$31:$T$36,$B2) * (1 + SUMIFS($X$7:$X$28,$T$7:$T$28,$A2)), 2)</f>
+        <f t="shared" ref="H2:H33" si="2">ROUND(SUMIFS(V$31:V$36,$S$31:$S$36,$B2) * (1 + SUMIFS($W$7:$W$28,$S$7:$S$28,$A2)), 2)</f>
         <v>6.2</v>
       </c>
-      <c r="I2" s="40">
-        <f>IF(ROUND(SUMIFS($AC$8:$AC$42, $AA$8:$AA$42,$A2,    $AB$8:$AB$42,$B2), 5)&gt;0, ROUND(SUMIFS($AC$8:$AC$42, $AA$8:$AA$42,$A2,    $AB$8:$AB$42,$B2), 5), "")</f>
+      <c r="I2" s="32">
+        <f t="shared" ref="I2:I33" si="3">IF(ROUND(SUMIFS($AA$8:$AA$42, $Y$8:$Y$42,$A2,    $Z$8:$Z$42,$B2), 5)&gt;0, ROUND(SUMIFS($AA$8:$AA$42, $Y$8:$Y$42,$A2,    $Z$8:$Z$42,$B2), 5), "")</f>
         <v>2.31E-3</v>
       </c>
-      <c r="J2" s="40">
+      <c r="J2" s="32">
         <f>I2</f>
         <v>2.31E-3</v>
       </c>
-      <c r="K2" s="39">
-        <f>IF(AND(ROUND(SUMIFS($AD$8:$AD$42, $AA$8:$AA$42,$A2,    $AB$8:$AB$42,$B2), 3)&gt;0, ROUND(SUMIFS($AD$8:$AD$42, $AA$8:$AA$42,$A2,    $AB$8:$AB$42,$B2), 3)&lt;1), ROUND(SUMIFS($AD$8:$AD$42, $AA$8:$AA$42,$A2,    $AB$8:$AB$42,$B2), 3), "")</f>
+      <c r="K2" s="33">
+        <f t="shared" ref="K2:K33" si="4">IF(SUMIFS($AF$7:$AF$19,    $AD$7:$AD$19,$A2,     $AE$7:$AE$19,$B2)&gt;0, SUMIFS($AF$7:$AF$19,    $AD$7:$AD$19,$A2,     $AE$7:$AE$19,$B2), "")</f>
+        <v>1334</v>
+      </c>
+      <c r="L2" s="33">
+        <f>IF(SUM(K2)&gt;0, 300, "")</f>
+        <v>300</v>
+      </c>
+      <c r="M2" s="31">
+        <f t="shared" ref="M2:M33" si="5">IF(AND(ROUND(SUMIFS($AB$8:$AB$42, $Y$8:$Y$42,$A2,    $Z$8:$Z$42,$B2), 3)&gt;0, ROUND(SUMIFS($AB$8:$AB$42, $Y$8:$Y$42,$A2,    $Z$8:$Z$42,$B2), 3)&lt;1), ROUND(SUMIFS($AB$8:$AB$42, $Y$8:$Y$42,$A2,    $Z$8:$Z$42,$B2), 3), "")</f>
         <v>0.92500000000000004</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -4156,42 +3972,50 @@
         <v>113.94</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F59" si="2">ROUND(SUMIFS(U$31:U$36,$T$31:$T$36,$B3) * (1 + SUMIFS($X$7:$X$28,$T$7:$T$28,$A3)), 2)</f>
+        <f t="shared" si="0"/>
         <v>2.2400000000000002</v>
       </c>
       <c r="G3">
-        <f t="shared" si="0"/>
-        <v>6.17</v>
-      </c>
-      <c r="H3">
         <f t="shared" si="1"/>
         <v>6.17</v>
       </c>
-      <c r="I3" s="40">
-        <f t="shared" ref="I3:I59" si="3">IF(ROUND(SUMIFS($AC$8:$AC$42, $AA$8:$AA$42,$A3,    $AB$8:$AB$42,$B3), 5)&gt;0, ROUND(SUMIFS($AC$8:$AC$42, $AA$8:$AA$42,$A3,    $AB$8:$AB$42,$B3), 5), "")</f>
+      <c r="H3">
+        <f t="shared" si="2"/>
+        <v>6.17</v>
+      </c>
+      <c r="I3" s="32">
+        <f t="shared" si="3"/>
         <v>4.4000000000000003E-3</v>
       </c>
-      <c r="J3" s="40">
-        <f t="shared" ref="J3:J59" si="4">I3</f>
+      <c r="J3" s="32">
+        <f t="shared" ref="J3:J59" si="6">I3</f>
         <v>4.4000000000000003E-3</v>
       </c>
-      <c r="K3" s="39">
-        <f t="shared" ref="K3:K59" si="5">IF(AND(ROUND(SUMIFS($AD$8:$AD$42, $AA$8:$AA$42,$A3,    $AB$8:$AB$42,$B3), 3)&gt;0, ROUND(SUMIFS($AD$8:$AD$42, $AA$8:$AA$42,$A3,    $AB$8:$AB$42,$B3), 3)&lt;1), ROUND(SUMIFS($AD$8:$AD$42, $AA$8:$AA$42,$A3,    $AB$8:$AB$42,$B3), 3), "")</f>
+      <c r="K3" s="33" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L3" s="33" t="str">
+        <f t="shared" ref="L3:L59" si="7">IF(SUM(K3)&gt;0, 300, "")</f>
+        <v/>
+      </c>
+      <c r="M3" s="31">
+        <f t="shared" si="5"/>
         <v>0.28699999999999998</v>
       </c>
-      <c r="AA3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="Y3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -4200,39 +4024,47 @@
         <v>4031</v>
       </c>
       <c r="F4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.91</v>
       </c>
       <c r="G4">
-        <f t="shared" si="0"/>
-        <v>8.01</v>
-      </c>
-      <c r="H4">
         <f t="shared" si="1"/>
         <v>8.01</v>
       </c>
-      <c r="I4" s="40">
+      <c r="H4">
+        <f t="shared" si="2"/>
+        <v>8.01</v>
+      </c>
+      <c r="I4" s="32">
         <f t="shared" si="3"/>
         <v>4.1599999999999996E-3</v>
       </c>
-      <c r="J4" s="40">
+      <c r="J4" s="32">
+        <f t="shared" si="6"/>
+        <v>4.1599999999999996E-3</v>
+      </c>
+      <c r="K4" s="33" t="str">
         <f t="shared" si="4"/>
-        <v>4.1599999999999996E-3</v>
-      </c>
-      <c r="K4" s="39">
+        <v/>
+      </c>
+      <c r="L4" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M4" s="31">
         <f t="shared" si="5"/>
         <v>0.76900000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -4241,39 +4073,47 @@
         <v>4036</v>
       </c>
       <c r="F5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.2200000000000002</v>
       </c>
       <c r="G5">
-        <f t="shared" si="0"/>
-        <v>6.09</v>
-      </c>
-      <c r="H5">
         <f t="shared" si="1"/>
         <v>6.09</v>
       </c>
-      <c r="I5" s="40">
+      <c r="H5">
+        <f t="shared" si="2"/>
+        <v>6.09</v>
+      </c>
+      <c r="I5" s="32">
         <f t="shared" si="3"/>
         <v>2.9499999999999999E-3</v>
       </c>
-      <c r="J5" s="40">
+      <c r="J5" s="32">
+        <f t="shared" si="6"/>
+        <v>2.9499999999999999E-3</v>
+      </c>
+      <c r="K5" s="33">
         <f t="shared" si="4"/>
-        <v>2.9499999999999999E-3</v>
-      </c>
-      <c r="K5" s="39">
+        <v>540</v>
+      </c>
+      <c r="L5" s="33">
+        <f t="shared" si="7"/>
+        <v>300</v>
+      </c>
+      <c r="M5" s="31">
         <f t="shared" si="5"/>
         <v>0.61399999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:33" ht="21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:34" ht="21" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -4282,54 +4122,68 @@
         <v>3300</v>
       </c>
       <c r="F6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.83</v>
       </c>
       <c r="G6">
-        <f t="shared" si="0"/>
-        <v>5.04</v>
-      </c>
-      <c r="H6">
         <f t="shared" si="1"/>
         <v>5.04</v>
       </c>
-      <c r="I6" s="40">
+      <c r="H6">
+        <f t="shared" si="2"/>
+        <v>5.04</v>
+      </c>
+      <c r="I6" s="32">
         <f t="shared" si="3"/>
         <v>3.3700000000000002E-3</v>
       </c>
-      <c r="J6" s="40">
+      <c r="J6" s="32">
+        <f t="shared" si="6"/>
+        <v>3.3700000000000002E-3</v>
+      </c>
+      <c r="K6" s="33">
         <f t="shared" si="4"/>
-        <v>3.3700000000000002E-3</v>
-      </c>
-      <c r="K6" s="39">
+        <v>270</v>
+      </c>
+      <c r="L6" s="33">
+        <f t="shared" si="7"/>
+        <v>300</v>
+      </c>
+      <c r="M6" s="31">
         <f t="shared" si="5"/>
         <v>0.75800000000000001</v>
       </c>
+      <c r="T6" t="s">
+        <v>38</v>
+      </c>
       <c r="U6" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="V6" t="s">
-        <v>92</v>
-      </c>
-      <c r="W6" t="s">
-        <v>93</v>
-      </c>
-      <c r="X6" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="AA6" s="34" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="W6" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y6" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF6" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -4338,70 +4192,87 @@
         <v>13614</v>
       </c>
       <c r="F7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.11</v>
       </c>
       <c r="G7">
-        <f t="shared" si="0"/>
-        <v>5.8</v>
-      </c>
-      <c r="H7">
         <f t="shared" si="1"/>
         <v>5.8</v>
       </c>
-      <c r="I7" s="40">
+      <c r="H7">
+        <f t="shared" si="2"/>
+        <v>5.8</v>
+      </c>
+      <c r="I7" s="32">
         <f t="shared" si="3"/>
         <v>7.5500000000000003E-3</v>
       </c>
-      <c r="J7" s="40">
+      <c r="J7" s="32">
+        <f t="shared" si="6"/>
+        <v>7.5500000000000003E-3</v>
+      </c>
+      <c r="K7" s="33">
         <f t="shared" si="4"/>
-        <v>7.5500000000000003E-3</v>
-      </c>
-      <c r="K7" s="39">
+        <v>980</v>
+      </c>
+      <c r="L7" s="33">
+        <f t="shared" si="7"/>
+        <v>300</v>
+      </c>
+      <c r="M7" s="31">
         <f t="shared" si="5"/>
         <v>0.76100000000000001</v>
       </c>
-      <c r="T7" s="5" t="s">
+      <c r="S7" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="U7" s="6">
+      <c r="T7" s="6">
         <f>'[1]vomcost mult'!O11</f>
         <v>45140</v>
       </c>
-      <c r="V7" s="28">
+      <c r="U7" s="20">
         <f>'[1]vomcost mult'!P11</f>
         <v>0.12757648618174755</v>
       </c>
-      <c r="W7" s="6">
+      <c r="V7" s="6">
         <f>'[1]vomcost mult'!Q11</f>
         <v>1</v>
       </c>
-      <c r="X7" s="29">
+      <c r="W7" s="21">
         <f>'[1]vomcost mult'!R11</f>
         <v>0.128</v>
       </c>
-      <c r="AA7" s="37" t="s">
-        <v>126</v>
+      <c r="Y7" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>75</v>
       </c>
       <c r="AB7" t="s">
-        <v>127</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="AD7" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>55</v>
+      </c>
+      <c r="AF7">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -4410,70 +4281,87 @@
         <v>128</v>
       </c>
       <c r="F8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.53</v>
       </c>
       <c r="G8">
-        <f t="shared" si="0"/>
-        <v>4.22</v>
-      </c>
-      <c r="H8">
         <f t="shared" si="1"/>
         <v>4.22</v>
       </c>
-      <c r="I8" s="40">
+      <c r="H8">
+        <f t="shared" si="2"/>
+        <v>4.22</v>
+      </c>
+      <c r="I8" s="32">
         <f t="shared" si="3"/>
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="J8" s="40">
+      <c r="J8" s="32">
+        <f t="shared" si="6"/>
+        <v>9.4999999999999998E-3</v>
+      </c>
+      <c r="K8" s="33">
         <f t="shared" si="4"/>
-        <v>9.4999999999999998E-3</v>
-      </c>
-      <c r="K8" s="39">
+        <v>14</v>
+      </c>
+      <c r="L8" s="33">
+        <f t="shared" si="7"/>
+        <v>300</v>
+      </c>
+      <c r="M8" s="31">
         <f t="shared" si="5"/>
         <v>0.82199999999999995</v>
       </c>
-      <c r="T8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="U8" s="6">
+      <c r="S8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8" s="6">
         <f>'[1]vomcost mult'!O12</f>
         <v>44440</v>
       </c>
-      <c r="V8" s="28">
+      <c r="U8" s="20">
         <f>'[1]vomcost mult'!P12</f>
         <v>0.12078898170883434</v>
       </c>
-      <c r="W8" s="6">
+      <c r="V8" s="6">
         <f>'[1]vomcost mult'!Q12</f>
         <v>1</v>
       </c>
-      <c r="X8" s="29">
+      <c r="W8" s="21">
         <f>'[1]vomcost mult'!R12</f>
         <v>0.121</v>
       </c>
-      <c r="AA8" s="37" t="s">
+      <c r="Y8" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="AB8" t="s">
-        <v>102</v>
-      </c>
-      <c r="AC8">
+      <c r="Z8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA8">
         <v>2.31E-3</v>
       </c>
-      <c r="AD8">
+      <c r="AB8">
         <v>0.92500000000000004</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AD8" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>55</v>
+      </c>
+      <c r="AF8">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -4482,70 +4370,87 @@
         <v>1557</v>
       </c>
       <c r="F9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.4</v>
       </c>
       <c r="G9">
-        <f t="shared" si="0"/>
-        <v>3.86</v>
-      </c>
-      <c r="H9">
         <f t="shared" si="1"/>
         <v>3.86</v>
       </c>
-      <c r="I9" s="40">
+      <c r="H9">
+        <f t="shared" si="2"/>
+        <v>3.86</v>
+      </c>
+      <c r="I9" s="32">
         <f t="shared" si="3"/>
         <v>6.4700000000000001E-3</v>
       </c>
-      <c r="J9" s="40">
+      <c r="J9" s="32">
+        <f t="shared" si="6"/>
+        <v>6.4700000000000001E-3</v>
+      </c>
+      <c r="K9" s="33" t="str">
         <f t="shared" si="4"/>
-        <v>6.4700000000000001E-3</v>
-      </c>
-      <c r="K9" s="39">
+        <v/>
+      </c>
+      <c r="L9" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M9" s="31">
         <f t="shared" si="5"/>
         <v>0.92</v>
       </c>
-      <c r="T9" s="5" t="s">
+      <c r="S9" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="U9" s="6">
+      <c r="T9" s="6">
         <f>'[1]vomcost mult'!O13</f>
         <v>96081</v>
       </c>
-      <c r="V9" s="28">
+      <c r="U9" s="20">
         <f>'[1]vomcost mult'!P13</f>
         <v>0.4556524459454061</v>
       </c>
-      <c r="W9" s="6">
+      <c r="V9" s="6">
         <f>'[1]vomcost mult'!Q13</f>
         <v>1</v>
       </c>
-      <c r="X9" s="29">
+      <c r="W9" s="21">
         <f>'[1]vomcost mult'!R13</f>
         <v>0.45600000000000002</v>
       </c>
-      <c r="AA9" s="37" t="s">
+      <c r="Y9" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="AB9" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC9">
+      <c r="Z9" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA9">
         <v>5.0499999999999998E-3</v>
       </c>
-      <c r="AD9">
+      <c r="AB9">
         <v>0.69099999999999995</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AD9" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>55</v>
+      </c>
+      <c r="AF9">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -4554,70 +4459,87 @@
         <v>38</v>
       </c>
       <c r="F10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.36</v>
       </c>
       <c r="G10">
-        <f t="shared" si="0"/>
-        <v>6.49</v>
-      </c>
-      <c r="H10">
         <f t="shared" si="1"/>
         <v>6.49</v>
       </c>
-      <c r="I10" s="40" t="str">
+      <c r="H10">
+        <f t="shared" si="2"/>
+        <v>6.49</v>
+      </c>
+      <c r="I10" s="32" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J10" s="40" t="str">
+      <c r="J10" s="32" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="K10" s="33" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K10" s="39" t="str">
+      <c r="L10" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M10" s="31" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="T10" s="5" t="s">
+      <c r="S10" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="U10" s="6">
+      <c r="T10" s="6">
         <f>'[1]vomcost mult'!O14</f>
         <v>43110</v>
       </c>
-      <c r="V10" s="28">
+      <c r="U10" s="20">
         <f>'[1]vomcost mult'!P14</f>
         <v>0.1075929542938924</v>
       </c>
-      <c r="W10" s="6">
+      <c r="V10" s="6">
         <f>'[1]vomcost mult'!Q14</f>
         <v>1</v>
       </c>
-      <c r="X10" s="29">
+      <c r="W10" s="21">
         <f>'[1]vomcost mult'!R14</f>
         <v>0.108</v>
       </c>
-      <c r="AA10" s="37" t="s">
+      <c r="Y10" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="AB10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AC10">
+      <c r="Z10" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA10">
         <v>7.7299999999999999E-3</v>
       </c>
-      <c r="AD10">
+      <c r="AB10">
         <v>0.626</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AD10" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF10">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -4626,70 +4548,87 @@
         <v>506.5</v>
       </c>
       <c r="F11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.38</v>
       </c>
       <c r="G11">
-        <f t="shared" si="0"/>
-        <v>3.8</v>
-      </c>
-      <c r="H11">
         <f t="shared" si="1"/>
         <v>3.8</v>
       </c>
-      <c r="I11" s="40">
+      <c r="H11">
+        <f t="shared" si="2"/>
+        <v>3.8</v>
+      </c>
+      <c r="I11" s="32">
         <f t="shared" si="3"/>
         <v>3.7100000000000002E-3</v>
       </c>
-      <c r="J11" s="40">
+      <c r="J11" s="32">
+        <f t="shared" si="6"/>
+        <v>3.7100000000000002E-3</v>
+      </c>
+      <c r="K11" s="33" t="str">
         <f t="shared" si="4"/>
-        <v>3.7100000000000002E-3</v>
-      </c>
-      <c r="K11" s="39">
+        <v/>
+      </c>
+      <c r="L11" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M11" s="31">
         <f t="shared" si="5"/>
         <v>0.82799999999999996</v>
       </c>
-      <c r="T11" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="U11" s="6">
+      <c r="S11" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="T11" s="6">
         <f>'[1]vomcost mult'!O15</f>
         <v>58160</v>
       </c>
-      <c r="V11" s="28">
+      <c r="U11" s="20">
         <f>'[1]vomcost mult'!P15</f>
         <v>0.2376393292909858</v>
       </c>
-      <c r="W11" s="6">
+      <c r="V11" s="6">
         <f>'[1]vomcost mult'!Q15</f>
         <v>1.05</v>
       </c>
-      <c r="X11" s="29">
+      <c r="W11" s="21">
         <f>'[1]vomcost mult'!R15</f>
         <v>0.25</v>
       </c>
-      <c r="AA11" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>102</v>
-      </c>
-      <c r="AC11">
+      <c r="Y11" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA11">
         <v>4.4000000000000003E-3</v>
       </c>
-      <c r="AD11">
+      <c r="AB11">
         <v>0.28699999999999998</v>
       </c>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AD11" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF11">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -4698,70 +4637,87 @@
         <v>1826</v>
       </c>
       <c r="F12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.33</v>
       </c>
       <c r="G12">
-        <f t="shared" si="0"/>
-        <v>6.41</v>
-      </c>
-      <c r="H12">
         <f t="shared" si="1"/>
         <v>6.41</v>
       </c>
-      <c r="I12" s="40" t="str">
+      <c r="H12">
+        <f t="shared" si="2"/>
+        <v>6.41</v>
+      </c>
+      <c r="I12" s="32" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J12" s="40" t="str">
+      <c r="J12" s="32" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="K12" s="33" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K12" s="39" t="str">
+      <c r="L12" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M12" s="31" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="T12" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="U12" s="6">
+      <c r="S12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="T12" s="6">
         <f>'[1]vomcost mult'!O16</f>
         <v>58160</v>
       </c>
-      <c r="V12" s="28">
+      <c r="U12" s="20">
         <f>'[1]vomcost mult'!P16</f>
         <v>0.2376393292909858</v>
       </c>
-      <c r="W12" s="6">
+      <c r="V12" s="6">
         <f>'[1]vomcost mult'!Q16</f>
         <v>1</v>
       </c>
-      <c r="X12" s="29">
+      <c r="W12" s="21">
         <f>'[1]vomcost mult'!R16</f>
         <v>0.23799999999999999</v>
       </c>
-      <c r="AA12" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>110</v>
-      </c>
-      <c r="AC12">
+      <c r="Y12" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA12">
         <v>1.3140000000000001E-2</v>
       </c>
-      <c r="AD12">
+      <c r="AB12">
         <v>0.84899999999999998</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AD12" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF12">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -4770,70 +4726,87 @@
         <v>2429.5540000000001</v>
       </c>
       <c r="F13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.0299999999999998</v>
       </c>
       <c r="G13">
-        <f t="shared" si="0"/>
-        <v>5.64</v>
-      </c>
-      <c r="H13">
         <f t="shared" si="1"/>
         <v>5.64</v>
       </c>
-      <c r="I13" s="40">
+      <c r="H13">
+        <f t="shared" si="2"/>
+        <v>5.64</v>
+      </c>
+      <c r="I13" s="32">
         <f t="shared" si="3"/>
         <v>5.0499999999999998E-3</v>
       </c>
-      <c r="J13" s="40">
+      <c r="J13" s="32">
+        <f t="shared" si="6"/>
+        <v>5.0499999999999998E-3</v>
+      </c>
+      <c r="K13" s="33" t="str">
         <f t="shared" si="4"/>
-        <v>5.0499999999999998E-3</v>
-      </c>
-      <c r="K13" s="39">
+        <v/>
+      </c>
+      <c r="L13" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M13" s="31">
         <f t="shared" si="5"/>
         <v>0.69099999999999995</v>
       </c>
-      <c r="T13" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="U13" s="6">
+      <c r="S13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="T13" s="6">
         <f>'[1]vomcost mult'!O17</f>
         <v>21060</v>
       </c>
-      <c r="V13" s="28">
+      <c r="U13" s="20">
         <f>'[1]vomcost mult'!P17</f>
         <v>-0.20352670171052795</v>
       </c>
-      <c r="W13" s="6">
+      <c r="V13" s="6">
         <f>'[1]vomcost mult'!Q17</f>
         <v>1</v>
       </c>
-      <c r="X13" s="29">
+      <c r="W13" s="21">
         <f>'[1]vomcost mult'!R17</f>
         <v>-0.20399999999999999</v>
       </c>
-      <c r="AA13" s="37" t="s">
+      <c r="Y13" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="AB13" t="s">
-        <v>102</v>
-      </c>
-      <c r="AC13">
+      <c r="Z13" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA13">
         <v>4.1599999999999996E-3</v>
       </c>
-      <c r="AD13">
+      <c r="AB13">
         <v>0.76900000000000002</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AD13" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF13">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -4842,70 +4815,87 @@
         <v>8152</v>
       </c>
       <c r="F14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.62</v>
       </c>
       <c r="G14">
-        <f t="shared" si="0"/>
-        <v>7.28</v>
-      </c>
-      <c r="H14">
         <f t="shared" si="1"/>
         <v>7.28</v>
       </c>
-      <c r="I14" s="40">
+      <c r="H14">
+        <f t="shared" si="2"/>
+        <v>7.28</v>
+      </c>
+      <c r="I14" s="32">
         <f t="shared" si="3"/>
         <v>5.7800000000000004E-3</v>
       </c>
-      <c r="J14" s="40">
+      <c r="J14" s="32">
+        <f t="shared" si="6"/>
+        <v>5.7800000000000004E-3</v>
+      </c>
+      <c r="K14" s="33" t="str">
         <f t="shared" si="4"/>
-        <v>5.7800000000000004E-3</v>
-      </c>
-      <c r="K14" s="39">
+        <v/>
+      </c>
+      <c r="L14" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M14" s="31">
         <f t="shared" si="5"/>
         <v>0.71699999999999997</v>
       </c>
-      <c r="T14" s="5" t="s">
+      <c r="S14" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="U14" s="6">
+      <c r="T14" s="6">
         <f>'[1]vomcost mult'!O18</f>
         <v>27800</v>
       </c>
-      <c r="V14" s="28">
+      <c r="U14" s="20">
         <f>'[1]vomcost mult'!P18</f>
         <v>-8.2940272641919402E-2</v>
       </c>
-      <c r="W14" s="6">
+      <c r="V14" s="6">
         <f>'[1]vomcost mult'!Q18</f>
         <v>1</v>
       </c>
-      <c r="X14" s="29">
+      <c r="W14" s="21">
         <f>'[1]vomcost mult'!R18</f>
         <v>-8.3000000000000004E-2</v>
       </c>
-      <c r="AA14" s="37" t="s">
+      <c r="Y14" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="AB14" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC14">
+      <c r="Z14" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA14">
         <v>5.7800000000000004E-3</v>
       </c>
-      <c r="AD14">
+      <c r="AB14">
         <v>0.71699999999999997</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AD14" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -4914,70 +4904,87 @@
         <v>1297</v>
       </c>
       <c r="F15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.99</v>
       </c>
       <c r="G15">
-        <f t="shared" si="0"/>
-        <v>5.54</v>
-      </c>
-      <c r="H15">
         <f t="shared" si="1"/>
         <v>5.54</v>
       </c>
-      <c r="I15" s="40">
+      <c r="H15">
+        <f t="shared" si="2"/>
+        <v>5.54</v>
+      </c>
+      <c r="I15" s="32">
         <f t="shared" si="3"/>
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="J15" s="40">
+      <c r="J15" s="32">
+        <f t="shared" si="6"/>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="K15" s="33" t="str">
         <f t="shared" si="4"/>
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="K15" s="39">
+        <v/>
+      </c>
+      <c r="L15" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M15" s="31">
         <f t="shared" si="5"/>
         <v>0.71299999999999997</v>
       </c>
-      <c r="T15" s="5" t="s">
+      <c r="S15" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="U15" s="6">
+      <c r="T15" s="6">
         <f>'[1]vomcost mult'!O19</f>
         <v>43110</v>
       </c>
-      <c r="V15" s="28">
+      <c r="U15" s="20">
         <f>'[1]vomcost mult'!P19</f>
         <v>0.1075929542938924</v>
       </c>
-      <c r="W15" s="6">
+      <c r="V15" s="6">
         <f>'[1]vomcost mult'!Q19</f>
         <v>1</v>
       </c>
-      <c r="X15" s="29">
+      <c r="W15" s="21">
         <f>'[1]vomcost mult'!R19</f>
         <v>0.108</v>
       </c>
-      <c r="AA15" s="37" t="s">
+      <c r="Y15" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="AB15" t="s">
-        <v>110</v>
-      </c>
-      <c r="AC15">
+      <c r="Z15" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA15">
         <v>5.6600000000000001E-3</v>
       </c>
-      <c r="AD15">
+      <c r="AB15">
         <v>0.59299999999999997</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AD15" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF15">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -4986,70 +4993,87 @@
         <v>10970</v>
       </c>
       <c r="F16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.65</v>
       </c>
       <c r="G16">
-        <f t="shared" si="0"/>
-        <v>4.59</v>
-      </c>
-      <c r="H16">
         <f t="shared" si="1"/>
         <v>4.59</v>
       </c>
-      <c r="I16" s="40">
+      <c r="H16">
+        <f t="shared" si="2"/>
+        <v>4.59</v>
+      </c>
+      <c r="I16" s="32">
         <f t="shared" si="3"/>
         <v>3.63E-3</v>
       </c>
-      <c r="J16" s="40">
+      <c r="J16" s="32">
+        <f t="shared" si="6"/>
+        <v>3.63E-3</v>
+      </c>
+      <c r="K16" s="33">
         <f t="shared" si="4"/>
-        <v>3.63E-3</v>
-      </c>
-      <c r="K16" s="39">
+        <v>104</v>
+      </c>
+      <c r="L16" s="33">
+        <f t="shared" si="7"/>
+        <v>300</v>
+      </c>
+      <c r="M16" s="31">
         <f t="shared" si="5"/>
         <v>0.61099999999999999</v>
       </c>
-      <c r="T16" s="5" t="s">
+      <c r="S16" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="U16" s="6">
+      <c r="T16" s="6">
         <f>'[1]vomcost mult'!O20</f>
         <v>38110</v>
       </c>
-      <c r="V16" s="28">
+      <c r="U16" s="20">
         <f>'[1]vomcost mult'!P20</f>
         <v>5.4053880212171543E-2</v>
       </c>
-      <c r="W16" s="6">
+      <c r="V16" s="6">
         <f>'[1]vomcost mult'!Q20</f>
         <v>1</v>
       </c>
-      <c r="X16" s="29">
+      <c r="W16" s="21">
         <f>'[1]vomcost mult'!R20</f>
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="AA16" s="37" t="s">
+      <c r="Y16" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="AB16" t="s">
-        <v>102</v>
-      </c>
-      <c r="AC16">
+      <c r="Z16" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA16">
         <v>2.9499999999999999E-3</v>
       </c>
-      <c r="AD16">
+      <c r="AB16">
         <v>0.61399999999999999</v>
       </c>
-    </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AD16" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF16">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -5058,70 +5082,87 @@
         <v>3200</v>
       </c>
       <c r="F17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.99</v>
       </c>
       <c r="G17">
-        <f t="shared" si="0"/>
-        <v>5.54</v>
-      </c>
-      <c r="H17">
         <f t="shared" si="1"/>
         <v>5.54</v>
       </c>
-      <c r="I17" s="40">
+      <c r="H17">
+        <f t="shared" si="2"/>
+        <v>5.54</v>
+      </c>
+      <c r="I17" s="32">
         <f t="shared" si="3"/>
         <v>3.8500000000000001E-3</v>
       </c>
-      <c r="J17" s="40">
+      <c r="J17" s="32">
+        <f t="shared" si="6"/>
+        <v>3.8500000000000001E-3</v>
+      </c>
+      <c r="K17" s="33">
         <f t="shared" si="4"/>
-        <v>3.8500000000000001E-3</v>
-      </c>
-      <c r="K17" s="39">
+        <v>308</v>
+      </c>
+      <c r="L17" s="33">
+        <f t="shared" si="7"/>
+        <v>300</v>
+      </c>
+      <c r="M17" s="31">
         <f t="shared" si="5"/>
         <v>0.81100000000000005</v>
       </c>
-      <c r="T17" s="5" t="s">
+      <c r="S17" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="U17" s="6">
+      <c r="T17" s="6">
         <f>'[1]vomcost mult'!O21</f>
         <v>19690</v>
       </c>
-      <c r="V17" s="28">
+      <c r="U17" s="20">
         <f>'[1]vomcost mult'!P21</f>
         <v>-0.2327393524218774</v>
       </c>
-      <c r="W17" s="6">
+      <c r="V17" s="6">
         <f>'[1]vomcost mult'!Q21</f>
         <v>1</v>
       </c>
-      <c r="X17" s="29">
+      <c r="W17" s="21">
         <f>'[1]vomcost mult'!R21</f>
         <v>-0.23300000000000001</v>
       </c>
-      <c r="AA17" s="37" t="s">
+      <c r="Y17" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="AB17" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC17">
+      <c r="Z17" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA17">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="AD17">
+      <c r="AB17">
         <v>0.71299999999999997</v>
       </c>
-    </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AD17" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF17">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -5130,70 +5171,87 @@
         <v>8477</v>
       </c>
       <c r="F18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.9</v>
       </c>
       <c r="G18">
-        <f t="shared" si="0"/>
-        <v>5.27</v>
-      </c>
-      <c r="H18">
         <f t="shared" si="1"/>
         <v>5.27</v>
       </c>
-      <c r="I18" s="40">
+      <c r="H18">
+        <f t="shared" si="2"/>
+        <v>5.27</v>
+      </c>
+      <c r="I18" s="32">
         <f t="shared" si="3"/>
         <v>2.3700000000000001E-3</v>
       </c>
-      <c r="J18" s="40">
+      <c r="J18" s="32">
+        <f t="shared" si="6"/>
+        <v>2.3700000000000001E-3</v>
+      </c>
+      <c r="K18" s="33" t="str">
         <f t="shared" si="4"/>
-        <v>2.3700000000000001E-3</v>
-      </c>
-      <c r="K18" s="39">
+        <v/>
+      </c>
+      <c r="L18" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M18" s="31">
         <f t="shared" si="5"/>
         <v>0.58499999999999996</v>
       </c>
-      <c r="T18" s="5" t="s">
+      <c r="S18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="U18" s="6">
+      <c r="T18" s="6">
         <f>'[1]vomcost mult'!O22</f>
         <v>16910</v>
       </c>
-      <c r="V18" s="28">
+      <c r="U18" s="20">
         <f>'[1]vomcost mult'!P22</f>
         <v>-0.29884146096225389</v>
       </c>
-      <c r="W18" s="6">
+      <c r="V18" s="6">
         <f>'[1]vomcost mult'!Q22</f>
         <v>1</v>
       </c>
-      <c r="X18" s="29">
+      <c r="W18" s="21">
         <f>'[1]vomcost mult'!R22</f>
         <v>-0.29899999999999999</v>
       </c>
-      <c r="AA18" s="37" t="s">
+      <c r="Y18" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="AB18" t="s">
-        <v>108</v>
-      </c>
-      <c r="AC18">
+      <c r="Z18" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA18">
         <v>7.2399999999999999E-3</v>
       </c>
-      <c r="AD18">
+      <c r="AB18">
         <v>0.84799999999999998</v>
       </c>
-    </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AD18" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF18">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -5202,70 +5260,87 @@
         <v>183.8</v>
       </c>
       <c r="F19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.24</v>
       </c>
       <c r="G19">
-        <f t="shared" si="0"/>
-        <v>3.45</v>
-      </c>
-      <c r="H19">
         <f t="shared" si="1"/>
         <v>3.45</v>
       </c>
-      <c r="I19" s="40">
+      <c r="H19">
+        <f t="shared" si="2"/>
+        <v>3.45</v>
+      </c>
+      <c r="I19" s="32">
         <f t="shared" si="3"/>
         <v>7.5399999999999998E-3</v>
       </c>
-      <c r="J19" s="40">
+      <c r="J19" s="32">
+        <f t="shared" si="6"/>
+        <v>7.5399999999999998E-3</v>
+      </c>
+      <c r="K19" s="33" t="str">
         <f t="shared" si="4"/>
-        <v>7.5399999999999998E-3</v>
-      </c>
-      <c r="K19" s="39">
+        <v/>
+      </c>
+      <c r="L19" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M19" s="31">
         <f t="shared" si="5"/>
         <v>0.59499999999999997</v>
       </c>
-      <c r="T19" s="5" t="s">
+      <c r="S19" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="U19" s="6">
+      <c r="T19" s="6">
         <f>'[1]vomcost mult'!O23</f>
         <v>50880</v>
       </c>
-      <c r="V19" s="28">
+      <c r="U19" s="20">
         <f>'[1]vomcost mult'!P23</f>
         <v>0.17956203408036178</v>
       </c>
-      <c r="W19" s="6">
+      <c r="V19" s="6">
         <f>'[1]vomcost mult'!Q23</f>
         <v>1</v>
       </c>
-      <c r="X19" s="29">
+      <c r="W19" s="21">
         <f>'[1]vomcost mult'!R23</f>
         <v>0.18</v>
       </c>
-      <c r="AA19" s="37" t="s">
+      <c r="Y19" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="AB19" t="s">
-        <v>110</v>
-      </c>
-      <c r="AC19">
+      <c r="Z19" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA19">
         <v>7.2399999999999999E-3</v>
       </c>
-      <c r="AD19">
+      <c r="AB19">
         <v>0.84799999999999998</v>
       </c>
-    </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AD19" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF19">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -5274,70 +5349,78 @@
         <v>5315</v>
       </c>
       <c r="F20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.13</v>
       </c>
       <c r="G20">
-        <f t="shared" si="0"/>
-        <v>5.91</v>
-      </c>
-      <c r="H20">
         <f t="shared" si="1"/>
         <v>5.91</v>
       </c>
-      <c r="I20" s="40">
+      <c r="H20">
+        <f t="shared" si="2"/>
+        <v>5.91</v>
+      </c>
+      <c r="I20" s="32">
         <f t="shared" si="3"/>
         <v>5.1399999999999996E-3</v>
       </c>
-      <c r="J20" s="40">
+      <c r="J20" s="32">
+        <f t="shared" si="6"/>
+        <v>5.1399999999999996E-3</v>
+      </c>
+      <c r="K20" s="33">
         <f t="shared" si="4"/>
-        <v>5.1399999999999996E-3</v>
-      </c>
-      <c r="K20" s="39" t="str">
+        <v>250</v>
+      </c>
+      <c r="L20" s="33">
+        <f t="shared" si="7"/>
+        <v>300</v>
+      </c>
+      <c r="M20" s="31" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="T20" s="5" t="s">
+      <c r="S20" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="U20" s="6">
+      <c r="T20" s="6">
         <f>'[1]vomcost mult'!O24</f>
         <v>66460</v>
       </c>
-      <c r="V20" s="28">
+      <c r="U20" s="20">
         <f>'[1]vomcost mult'!P24</f>
         <v>0.2955752683826966</v>
       </c>
-      <c r="W20" s="6">
+      <c r="V20" s="6">
         <f>'[1]vomcost mult'!Q24</f>
         <v>1.05</v>
       </c>
-      <c r="X20" s="29">
+      <c r="W20" s="21">
         <f>'[1]vomcost mult'!R24</f>
         <v>0.31</v>
       </c>
-      <c r="AA20" s="37" t="s">
+      <c r="Y20" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="AB20" t="s">
-        <v>102</v>
-      </c>
-      <c r="AC20">
+      <c r="Z20" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA20">
         <v>3.3700000000000002E-3</v>
       </c>
-      <c r="AD20">
+      <c r="AB20">
         <v>0.75800000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -5346,70 +5429,78 @@
         <v>8055</v>
       </c>
       <c r="F21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.11</v>
       </c>
       <c r="G21">
-        <f t="shared" si="0"/>
-        <v>5.87</v>
-      </c>
-      <c r="H21">
         <f t="shared" si="1"/>
         <v>5.87</v>
       </c>
-      <c r="I21" s="40">
+      <c r="H21">
+        <f t="shared" si="2"/>
+        <v>5.87</v>
+      </c>
+      <c r="I21" s="32">
         <f t="shared" si="3"/>
         <v>5.5599999999999998E-3</v>
       </c>
-      <c r="J21" s="40">
+      <c r="J21" s="32">
+        <f t="shared" si="6"/>
+        <v>5.5599999999999998E-3</v>
+      </c>
+      <c r="K21" s="33">
         <f t="shared" si="4"/>
-        <v>5.5599999999999998E-3</v>
-      </c>
-      <c r="K21" s="39" t="str">
+        <v>824</v>
+      </c>
+      <c r="L21" s="33">
+        <f t="shared" si="7"/>
+        <v>300</v>
+      </c>
+      <c r="M21" s="31" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="T21" s="5" t="s">
+      <c r="S21" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="U21" s="6">
+      <c r="T21" s="6">
         <f>'[1]vomcost mult'!O25</f>
         <v>66460</v>
       </c>
-      <c r="V21" s="28">
+      <c r="U21" s="20">
         <f>'[1]vomcost mult'!P25</f>
         <v>0.2955752683826966</v>
       </c>
-      <c r="W21" s="6">
+      <c r="V21" s="6">
         <f>'[1]vomcost mult'!Q25</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="X21" s="29">
+      <c r="W21" s="21">
         <f>'[1]vomcost mult'!R25</f>
         <v>0.32500000000000001</v>
       </c>
-      <c r="AA21" s="37" t="s">
+      <c r="Y21" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="AB21" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC21">
+      <c r="Z21" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA21">
         <v>3.63E-3</v>
       </c>
-      <c r="AD21">
+      <c r="AB21">
         <v>0.61099999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -5418,70 +5509,78 @@
         <v>2331</v>
       </c>
       <c r="F22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.1</v>
       </c>
       <c r="G22">
-        <f t="shared" si="0"/>
-        <v>5.83</v>
-      </c>
-      <c r="H22">
         <f t="shared" si="1"/>
         <v>5.83</v>
       </c>
-      <c r="I22" s="40">
+      <c r="H22">
+        <f t="shared" si="2"/>
+        <v>5.83</v>
+      </c>
+      <c r="I22" s="32">
         <f t="shared" si="3"/>
         <v>6.4799999999999996E-3</v>
       </c>
-      <c r="J22" s="40">
+      <c r="J22" s="32">
+        <f t="shared" si="6"/>
+        <v>6.4799999999999996E-3</v>
+      </c>
+      <c r="K22" s="33">
         <f t="shared" si="4"/>
-        <v>6.4799999999999996E-3</v>
-      </c>
-      <c r="K22" s="39" t="str">
+        <v>108</v>
+      </c>
+      <c r="L22" s="33">
+        <f t="shared" si="7"/>
+        <v>300</v>
+      </c>
+      <c r="M22" s="31" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="T22" s="5" t="s">
+      <c r="S22" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="U22" s="6">
+      <c r="T22" s="6">
         <f>'[1]vomcost mult'!O26</f>
         <v>66460</v>
       </c>
-      <c r="V22" s="28">
+      <c r="U22" s="20">
         <f>'[1]vomcost mult'!P26</f>
         <v>0.2955752683826966</v>
       </c>
-      <c r="W22" s="6">
+      <c r="V22" s="6">
         <f>'[1]vomcost mult'!Q26</f>
         <v>1</v>
       </c>
-      <c r="X22" s="29">
+      <c r="W22" s="21">
         <f>'[1]vomcost mult'!R26</f>
         <v>0.29599999999999999</v>
       </c>
-      <c r="AA22" s="37" t="s">
+      <c r="Y22" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="AB22" t="s">
-        <v>108</v>
-      </c>
-      <c r="AC22">
+      <c r="Z22" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA22">
         <v>8.0999999999999996E-3</v>
       </c>
-      <c r="AD22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AB22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -5490,70 +5589,78 @@
         <v>237</v>
       </c>
       <c r="F23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.08</v>
       </c>
       <c r="G23">
-        <f t="shared" si="0"/>
-        <v>5.79</v>
-      </c>
-      <c r="H23">
         <f t="shared" si="1"/>
         <v>5.79</v>
       </c>
-      <c r="I23" s="40">
+      <c r="H23">
+        <f t="shared" si="2"/>
+        <v>5.79</v>
+      </c>
+      <c r="I23" s="32">
         <f t="shared" si="3"/>
         <v>8.9899999999999997E-3</v>
       </c>
-      <c r="J23" s="40">
+      <c r="J23" s="32">
+        <f t="shared" si="6"/>
+        <v>8.9899999999999997E-3</v>
+      </c>
+      <c r="K23" s="33" t="str">
         <f t="shared" si="4"/>
-        <v>8.9899999999999997E-3</v>
-      </c>
-      <c r="K23" s="39" t="str">
+        <v/>
+      </c>
+      <c r="L23" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M23" s="31" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="T23" s="5" t="s">
+      <c r="S23" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="U23" s="6">
+      <c r="T23" s="6">
         <f>'[1]vomcost mult'!O27</f>
         <v>16470</v>
       </c>
-      <c r="V23" s="28">
+      <c r="U23" s="20">
         <f>'[1]vomcost mult'!P27</f>
         <v>-0.31029146939024133</v>
       </c>
-      <c r="W23" s="6">
+      <c r="V23" s="6">
         <f>'[1]vomcost mult'!Q27</f>
         <v>1</v>
       </c>
-      <c r="X23" s="29">
+      <c r="W23" s="21">
         <f>'[1]vomcost mult'!R27</f>
         <v>-0.31</v>
       </c>
-      <c r="AA23" s="37" t="s">
+      <c r="Y23" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="AB23" t="s">
-        <v>110</v>
-      </c>
-      <c r="AC23">
+      <c r="Z23" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA23">
         <v>8.0999999999999996E-3</v>
       </c>
-      <c r="AD23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AB23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -5562,142 +5669,158 @@
         <v>3459.28</v>
       </c>
       <c r="F24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.2599999999999998</v>
       </c>
       <c r="G24">
-        <f t="shared" si="0"/>
-        <v>4.51</v>
-      </c>
-      <c r="H24">
         <f t="shared" si="1"/>
         <v>4.51</v>
       </c>
-      <c r="I24" s="40">
+      <c r="H24">
+        <f t="shared" si="2"/>
+        <v>4.51</v>
+      </c>
+      <c r="I24" s="32">
         <f t="shared" si="3"/>
         <v>7.7299999999999999E-3</v>
       </c>
-      <c r="J24" s="40">
+      <c r="J24" s="32">
+        <f t="shared" si="6"/>
+        <v>7.7299999999999999E-3</v>
+      </c>
+      <c r="K24" s="33" t="str">
         <f t="shared" si="4"/>
-        <v>7.7299999999999999E-3</v>
-      </c>
-      <c r="K24" s="39">
+        <v/>
+      </c>
+      <c r="L24" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M24" s="31">
         <f t="shared" si="5"/>
         <v>0.626</v>
       </c>
-      <c r="T24" s="5" t="s">
+      <c r="S24" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="U24" s="6">
+      <c r="T24" s="6">
         <f>'[1]vomcost mult'!O28</f>
         <v>48310</v>
       </c>
-      <c r="V24" s="28">
+      <c r="U24" s="20">
         <f>'[1]vomcost mult'!P28</f>
         <v>0.15705196892652412</v>
       </c>
-      <c r="W24" s="6">
+      <c r="V24" s="6">
         <f>'[1]vomcost mult'!Q28</f>
         <v>1.1499999999999999</v>
       </c>
-      <c r="X24" s="29">
+      <c r="W24" s="21">
         <f>'[1]vomcost mult'!R28</f>
         <v>0.18099999999999999</v>
       </c>
-      <c r="AA24" s="37" t="s">
+      <c r="Y24" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="AB24" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC24">
+      <c r="Z24" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA24">
         <v>3.8500000000000001E-3</v>
       </c>
-      <c r="AD24">
+      <c r="AB24">
         <v>0.81100000000000005</v>
       </c>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
       <c r="F25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.91</v>
       </c>
       <c r="G25">
-        <f t="shared" si="0"/>
-        <v>5.82</v>
-      </c>
-      <c r="H25">
         <f t="shared" si="1"/>
         <v>5.82</v>
       </c>
-      <c r="I25" s="40" t="str">
+      <c r="H25">
+        <f t="shared" si="2"/>
+        <v>5.82</v>
+      </c>
+      <c r="I25" s="32" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J25" s="40" t="str">
+      <c r="J25" s="32" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="K25" s="33" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K25" s="39" t="str">
+      <c r="L25" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M25" s="31" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="M25" t="s">
-        <v>38</v>
-      </c>
-      <c r="T25" s="5" t="s">
+      <c r="O25" t="s">
+        <v>34</v>
+      </c>
+      <c r="S25" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="U25" s="6">
+      <c r="T25" s="6">
         <f>'[1]vomcost mult'!O29</f>
         <v>48310</v>
       </c>
-      <c r="V25" s="28">
+      <c r="U25" s="20">
         <f>'[1]vomcost mult'!P29</f>
         <v>0.15705196892652412</v>
       </c>
-      <c r="W25" s="6">
+      <c r="V25" s="6">
         <f>'[1]vomcost mult'!Q29</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="X25" s="29">
+      <c r="W25" s="21">
         <f>'[1]vomcost mult'!R29</f>
         <v>0.17299999999999999</v>
       </c>
-      <c r="AA25" s="37" t="s">
+      <c r="Y25" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="AB25" t="s">
-        <v>102</v>
-      </c>
-      <c r="AC25">
+      <c r="Z25" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA25">
         <v>7.5500000000000003E-3</v>
       </c>
-      <c r="AD25">
+      <c r="AB25">
         <v>0.76100000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -5706,70 +5829,78 @@
         <v>1644</v>
       </c>
       <c r="F26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.2200000000000002</v>
       </c>
       <c r="G26">
-        <f t="shared" si="0"/>
-        <v>4.43</v>
-      </c>
-      <c r="H26">
         <f t="shared" si="1"/>
         <v>4.43</v>
       </c>
-      <c r="I26" s="40">
+      <c r="H26">
+        <f t="shared" si="2"/>
+        <v>4.43</v>
+      </c>
+      <c r="I26" s="32">
         <f t="shared" si="3"/>
         <v>7.2399999999999999E-3</v>
       </c>
-      <c r="J26" s="40">
+      <c r="J26" s="32">
+        <f t="shared" si="6"/>
+        <v>7.2399999999999999E-3</v>
+      </c>
+      <c r="K26" s="33" t="str">
         <f t="shared" si="4"/>
-        <v>7.2399999999999999E-3</v>
-      </c>
-      <c r="K26" s="39">
+        <v/>
+      </c>
+      <c r="L26" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M26" s="31">
         <f t="shared" si="5"/>
         <v>0.84799999999999998</v>
       </c>
-      <c r="T26" s="5" t="s">
+      <c r="S26" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="U26" s="6">
+      <c r="T26" s="6">
         <f>'[1]vomcost mult'!O30</f>
         <v>48310</v>
       </c>
-      <c r="V26" s="28">
+      <c r="U26" s="20">
         <f>'[1]vomcost mult'!P30</f>
         <v>0.15705196892652412</v>
       </c>
-      <c r="W26" s="6">
+      <c r="V26" s="6">
         <f>'[1]vomcost mult'!Q30</f>
         <v>1.05</v>
       </c>
-      <c r="X26" s="29">
+      <c r="W26" s="21">
         <f>'[1]vomcost mult'!R30</f>
         <v>0.16500000000000001</v>
       </c>
-      <c r="AA26" s="37" t="s">
+      <c r="Y26" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="AB26" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC26">
+      <c r="Z26" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA26">
         <v>2.3700000000000001E-3</v>
       </c>
-      <c r="AD26">
+      <c r="AB26">
         <v>0.58499999999999996</v>
       </c>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="C27" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -5778,70 +5909,78 @@
         <v>2683</v>
       </c>
       <c r="F27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.83</v>
       </c>
       <c r="G27">
-        <f t="shared" si="0"/>
-        <v>3.67</v>
-      </c>
-      <c r="H27">
         <f t="shared" si="1"/>
         <v>3.67</v>
       </c>
-      <c r="I27" s="40">
+      <c r="H27">
+        <f t="shared" si="2"/>
+        <v>3.67</v>
+      </c>
+      <c r="I27" s="32">
         <f t="shared" si="3"/>
         <v>8.0999999999999996E-3</v>
       </c>
-      <c r="J27" s="40">
+      <c r="J27" s="32">
+        <f t="shared" si="6"/>
+        <v>8.0999999999999996E-3</v>
+      </c>
+      <c r="K27" s="33" t="str">
         <f t="shared" si="4"/>
-        <v>8.0999999999999996E-3</v>
-      </c>
-      <c r="K27" s="39" t="str">
+        <v/>
+      </c>
+      <c r="L27" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M27" s="31" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="T27" s="5" t="s">
+      <c r="S27" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="U27" s="6">
+      <c r="T27" s="6">
         <f>'[1]vomcost mult'!O31</f>
         <v>48310</v>
       </c>
-      <c r="V27" s="28">
+      <c r="U27" s="20">
         <f>'[1]vomcost mult'!P31</f>
         <v>0.15705196892652412</v>
       </c>
-      <c r="W27" s="6">
+      <c r="V27" s="6">
         <f>'[1]vomcost mult'!Q31</f>
         <v>1</v>
       </c>
-      <c r="X27" s="29">
+      <c r="W27" s="21">
         <f>'[1]vomcost mult'!R31</f>
         <v>0.157</v>
       </c>
-      <c r="AA27" s="37" t="s">
+      <c r="Y27" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="AB27" t="s">
-        <v>108</v>
-      </c>
-      <c r="AC27">
+      <c r="Z27" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA27">
         <v>9.3799999999999994E-3</v>
       </c>
-      <c r="AD27">
+      <c r="AB27">
         <v>0.89300000000000002</v>
       </c>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="C28" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -5850,70 +5989,78 @@
         <v>1850</v>
       </c>
       <c r="F28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.11</v>
       </c>
       <c r="G28">
-        <f t="shared" si="0"/>
-        <v>4.22</v>
-      </c>
-      <c r="H28">
         <f t="shared" si="1"/>
         <v>4.22</v>
       </c>
-      <c r="I28" s="40">
+      <c r="H28">
+        <f t="shared" si="2"/>
+        <v>4.22</v>
+      </c>
+      <c r="I28" s="32">
         <f t="shared" si="3"/>
         <v>9.3799999999999994E-3</v>
       </c>
-      <c r="J28" s="40">
+      <c r="J28" s="32">
+        <f t="shared" si="6"/>
+        <v>9.3799999999999994E-3</v>
+      </c>
+      <c r="K28" s="33" t="str">
         <f t="shared" si="4"/>
-        <v>9.3799999999999994E-3</v>
-      </c>
-      <c r="K28" s="39">
+        <v/>
+      </c>
+      <c r="L28" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M28" s="31">
         <f t="shared" si="5"/>
         <v>0.89300000000000002</v>
       </c>
-      <c r="T28" s="5" t="s">
+      <c r="S28" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="U28" s="6">
+      <c r="T28" s="6">
         <f>'[1]vomcost mult'!O32</f>
         <v>49193</v>
       </c>
-      <c r="V28" s="28">
+      <c r="U28" s="20">
         <f>'[1]vomcost mult'!P32</f>
         <v>0.16491823994601576</v>
       </c>
-      <c r="W28" s="6">
+      <c r="V28" s="6">
         <f>'[1]vomcost mult'!Q32</f>
         <v>1</v>
       </c>
-      <c r="X28" s="29">
+      <c r="W28" s="21">
         <f>'[1]vomcost mult'!R32</f>
         <v>0.16500000000000001</v>
       </c>
-      <c r="AA28" s="37" t="s">
+      <c r="Y28" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="AB28" t="s">
-        <v>110</v>
-      </c>
-      <c r="AC28">
+      <c r="Z28" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA28">
         <v>9.3799999999999994E-3</v>
       </c>
-      <c r="AD28">
+      <c r="AB28">
         <v>0.89300000000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -5922,51 +6069,59 @@
         <v>4631.3999999999996</v>
       </c>
       <c r="F29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.62</v>
       </c>
       <c r="G29">
-        <f t="shared" si="0"/>
-        <v>5.24</v>
-      </c>
-      <c r="H29">
         <f t="shared" si="1"/>
         <v>5.24</v>
       </c>
-      <c r="I29" s="40">
+      <c r="H29">
+        <f t="shared" si="2"/>
+        <v>5.24</v>
+      </c>
+      <c r="I29" s="32">
         <f t="shared" si="3"/>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J29" s="40">
+      <c r="J29" s="32">
+        <f t="shared" si="6"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K29" s="33">
         <f t="shared" si="4"/>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="K29" s="39">
+        <v>324</v>
+      </c>
+      <c r="L29" s="33">
+        <f t="shared" si="7"/>
+        <v>300</v>
+      </c>
+      <c r="M29" s="31">
         <f t="shared" si="5"/>
         <v>0.95299999999999996</v>
       </c>
-      <c r="AA29" s="37" t="s">
+      <c r="Y29" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="AB29" t="s">
-        <v>102</v>
-      </c>
-      <c r="AC29">
+      <c r="Z29" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA29">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="AD29">
+      <c r="AB29">
         <v>0.82199999999999995</v>
       </c>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="C30" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -5975,60 +6130,68 @@
         <v>5540.4</v>
       </c>
       <c r="F30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.65</v>
       </c>
       <c r="G30">
-        <f t="shared" si="0"/>
-        <v>5.3</v>
-      </c>
-      <c r="H30">
         <f t="shared" si="1"/>
         <v>5.3</v>
       </c>
-      <c r="I30" s="40">
+      <c r="H30">
+        <f t="shared" si="2"/>
+        <v>5.3</v>
+      </c>
+      <c r="I30" s="32">
         <f t="shared" si="3"/>
         <v>6.5500000000000003E-3</v>
       </c>
-      <c r="J30" s="40">
+      <c r="J30" s="32">
+        <f t="shared" si="6"/>
+        <v>6.5500000000000003E-3</v>
+      </c>
+      <c r="K30" s="33">
         <f t="shared" si="4"/>
-        <v>6.5500000000000003E-3</v>
-      </c>
-      <c r="K30" s="39">
+        <v>381</v>
+      </c>
+      <c r="L30" s="33">
+        <f t="shared" si="7"/>
+        <v>300</v>
+      </c>
+      <c r="M30" s="31">
         <f t="shared" si="5"/>
         <v>0.92400000000000004</v>
       </c>
+      <c r="T30" t="s">
+        <v>37</v>
+      </c>
       <c r="U30" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="V30" t="s">
-        <v>98</v>
-      </c>
-      <c r="W30" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA30" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y30" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="AB30" t="s">
-        <v>110</v>
-      </c>
-      <c r="AC30">
+      <c r="Z30" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA30">
         <v>1.268E-2</v>
       </c>
-      <c r="AD30">
+      <c r="AB30">
         <v>0.99399999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="C31" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -6037,66 +6200,74 @@
         <v>23605.1</v>
       </c>
       <c r="F31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.59</v>
       </c>
       <c r="G31">
-        <f t="shared" si="0"/>
-        <v>5.18</v>
-      </c>
-      <c r="H31">
         <f t="shared" si="1"/>
         <v>5.18</v>
       </c>
-      <c r="I31" s="40">
+      <c r="H31">
+        <f t="shared" si="2"/>
+        <v>5.18</v>
+      </c>
+      <c r="I31" s="32">
         <f t="shared" si="3"/>
         <v>4.4799999999999996E-3</v>
       </c>
-      <c r="J31" s="40">
+      <c r="J31" s="32">
+        <f t="shared" si="6"/>
+        <v>4.4799999999999996E-3</v>
+      </c>
+      <c r="K31" s="33">
         <f t="shared" si="4"/>
-        <v>4.4799999999999996E-3</v>
-      </c>
-      <c r="K31" s="39">
+        <v>1031</v>
+      </c>
+      <c r="L31" s="33">
+        <f t="shared" si="7"/>
+        <v>300</v>
+      </c>
+      <c r="M31" s="31">
         <f t="shared" si="5"/>
         <v>0.95299999999999996</v>
       </c>
-      <c r="T31" t="s">
-        <v>102</v>
+      <c r="S31" t="s">
+        <v>49</v>
+      </c>
+      <c r="T31" s="8">
+        <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$D:$D, $S31)</f>
+        <v>2</v>
       </c>
       <c r="U31" s="8">
-        <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$D:$D, $T31)</f>
-        <v>2</v>
+        <f>SUMIFS([2]unittypedata!$Y:$Y,[2]unittypedata!$D:$D, $S31)</f>
+        <v>5.5</v>
       </c>
       <c r="V31" s="8">
-        <f>SUMIFS([2]unittypedata!$Y:$Y,[2]unittypedata!$D:$D, $T31)</f>
+        <f>SUMIFS([2]unittypedata!$Z:$Z,[2]unittypedata!$D:$D, $S31)</f>
         <v>5.5</v>
       </c>
-      <c r="W31" s="8">
-        <f>SUMIFS([2]unittypedata!$Z:$Z,[2]unittypedata!$D:$D, $T31)</f>
-        <v>5.5</v>
-      </c>
-      <c r="AA31" s="37" t="s">
+      <c r="Y31" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="AB31" t="s">
-        <v>102</v>
-      </c>
-      <c r="AC31">
+      <c r="Z31" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA31">
         <v>6.4700000000000001E-3</v>
       </c>
-      <c r="AD31">
+      <c r="AB31">
         <v>0.92</v>
       </c>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="C32" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -6105,66 +6276,74 @@
         <v>178.8</v>
       </c>
       <c r="F32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.38</v>
       </c>
       <c r="G32">
-        <f t="shared" si="0"/>
-        <v>2.76</v>
-      </c>
-      <c r="H32">
         <f t="shared" si="1"/>
         <v>2.76</v>
       </c>
-      <c r="I32" s="40">
+      <c r="H32">
+        <f t="shared" si="2"/>
+        <v>2.76</v>
+      </c>
+      <c r="I32" s="32">
         <f t="shared" si="3"/>
         <v>1.108E-2</v>
       </c>
-      <c r="J32" s="40">
+      <c r="J32" s="32">
+        <f t="shared" si="6"/>
+        <v>1.108E-2</v>
+      </c>
+      <c r="K32" s="33" t="str">
         <f t="shared" si="4"/>
-        <v>1.108E-2</v>
-      </c>
-      <c r="K32" s="39">
+        <v/>
+      </c>
+      <c r="L32" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M32" s="31">
         <f t="shared" si="5"/>
         <v>0.90500000000000003</v>
       </c>
-      <c r="T32" t="s">
-        <v>103</v>
+      <c r="S32" t="s">
+        <v>50</v>
+      </c>
+      <c r="T32" s="8">
+        <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$D:$D, $S32)</f>
+        <v>1.8</v>
       </c>
       <c r="U32" s="8">
-        <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$D:$D, $T32)</f>
-        <v>1.8</v>
+        <f>SUMIFS([2]unittypedata!$Y:$Y,[2]unittypedata!$D:$D, $S32)</f>
+        <v>5</v>
       </c>
       <c r="V32" s="8">
-        <f>SUMIFS([2]unittypedata!$Y:$Y,[2]unittypedata!$D:$D, $T32)</f>
+        <f>SUMIFS([2]unittypedata!$Z:$Z,[2]unittypedata!$D:$D, $S32)</f>
         <v>5</v>
       </c>
-      <c r="W32" s="8">
-        <f>SUMIFS([2]unittypedata!$Z:$Z,[2]unittypedata!$D:$D, $T32)</f>
-        <v>5</v>
-      </c>
-      <c r="AA32" s="37" t="s">
+      <c r="Y32" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="AB32" t="s">
-        <v>108</v>
-      </c>
-      <c r="AC32">
+      <c r="Z32" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA32">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="AD32">
+      <c r="AB32">
         <v>0.95299999999999996</v>
       </c>
     </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -6173,134 +6352,150 @@
         <v>2560</v>
       </c>
       <c r="F33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>1.8</v>
       </c>
       <c r="G33">
-        <f t="shared" si="0"/>
-        <v>3.95</v>
-      </c>
-      <c r="H33">
         <f t="shared" si="1"/>
         <v>3.95</v>
       </c>
-      <c r="I33" s="40" t="str">
+      <c r="H33">
+        <f t="shared" si="2"/>
+        <v>3.95</v>
+      </c>
+      <c r="I33" s="32" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J33" s="40" t="str">
+      <c r="J33" s="32" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="K33" s="33" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K33" s="39" t="str">
+      <c r="L33" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M33" s="31" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="T33" t="s">
-        <v>104</v>
+      <c r="S33" t="s">
+        <v>51</v>
+      </c>
+      <c r="T33" s="8">
+        <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$D:$D, $S33)</f>
+        <v>2</v>
       </c>
       <c r="U33" s="8">
-        <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$D:$D, $T33)</f>
-        <v>2</v>
+        <f>SUMIFS([2]unittypedata!$Y:$Y,[2]unittypedata!$D:$D, $S33)</f>
+        <v>4</v>
       </c>
       <c r="V33" s="8">
-        <f>SUMIFS([2]unittypedata!$Y:$Y,[2]unittypedata!$D:$D, $T33)</f>
+        <f>SUMIFS([2]unittypedata!$Z:$Z,[2]unittypedata!$D:$D, $S33)</f>
         <v>4</v>
       </c>
-      <c r="W33" s="8">
-        <f>SUMIFS([2]unittypedata!$Z:$Z,[2]unittypedata!$D:$D, $T33)</f>
-        <v>4</v>
-      </c>
-      <c r="AA33" s="37" t="s">
+      <c r="Y33" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="AB33" t="s">
-        <v>108</v>
-      </c>
-      <c r="AC33">
+      <c r="Z33" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA33">
         <v>6.5500000000000003E-3</v>
       </c>
-      <c r="AD33">
+      <c r="AB33">
         <v>0.92400000000000004</v>
       </c>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="C34" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D34">
         <v>1</v>
       </c>
       <c r="F34">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="F34:F59" si="8">ROUND(SUMIFS(T$31:T$36,$S$31:$S$36,$B34) * (1 + SUMIFS($W$7:$W$28,$S$7:$S$28,$A34)), 2)</f>
         <v>2.33</v>
       </c>
       <c r="G34">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="G34:G59" si="9">ROUND(SUMIFS(U$31:U$36,$S$31:$S$36,$B34) * (1 + SUMIFS($W$7:$W$28,$S$7:$S$28,$A34)), 2)</f>
         <v>5.0999999999999996</v>
       </c>
       <c r="H34">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="H34:H59" si="10">ROUND(SUMIFS(V$31:V$36,$S$31:$S$36,$B34) * (1 + SUMIFS($W$7:$W$28,$S$7:$S$28,$A34)), 2)</f>
         <v>5.0999999999999996</v>
       </c>
-      <c r="I34" s="40" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J34" s="40" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K34" s="39" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="M34" t="s">
-        <v>38</v>
-      </c>
-      <c r="T34" t="s">
-        <v>105</v>
+      <c r="I34" s="32" t="str">
+        <f t="shared" ref="I34:I59" si="11">IF(ROUND(SUMIFS($AA$8:$AA$42, $Y$8:$Y$42,$A34,    $Z$8:$Z$42,$B34), 5)&gt;0, ROUND(SUMIFS($AA$8:$AA$42, $Y$8:$Y$42,$A34,    $Z$8:$Z$42,$B34), 5), "")</f>
+        <v/>
+      </c>
+      <c r="J34" s="32" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="K34" s="33" t="str">
+        <f t="shared" ref="K34:K59" si="12">IF(SUMIFS($AF$7:$AF$19,    $AD$7:$AD$19,$A34,     $AE$7:$AE$19,$B34)&gt;0, SUMIFS($AF$7:$AF$19,    $AD$7:$AD$19,$A34,     $AE$7:$AE$19,$B34), "")</f>
+        <v/>
+      </c>
+      <c r="L34" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M34" s="31" t="str">
+        <f t="shared" ref="M34:M59" si="13">IF(AND(ROUND(SUMIFS($AB$8:$AB$42, $Y$8:$Y$42,$A34,    $Z$8:$Z$42,$B34), 3)&gt;0, ROUND(SUMIFS($AB$8:$AB$42, $Y$8:$Y$42,$A34,    $Z$8:$Z$42,$B34), 3)&lt;1), ROUND(SUMIFS($AB$8:$AB$42, $Y$8:$Y$42,$A34,    $Z$8:$Z$42,$B34), 3), "")</f>
+        <v/>
+      </c>
+      <c r="O34" t="s">
+        <v>34</v>
+      </c>
+      <c r="S34" t="s">
+        <v>52</v>
+      </c>
+      <c r="T34" s="8">
+        <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$D:$D, $S34)</f>
+        <v>1.6</v>
       </c>
       <c r="U34" s="8">
-        <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$D:$D, $T34)</f>
-        <v>1.6</v>
+        <f>SUMIFS([2]unittypedata!$Y:$Y,[2]unittypedata!$D:$D, $S34)</f>
+        <v>3.5</v>
       </c>
       <c r="V34" s="8">
-        <f>SUMIFS([2]unittypedata!$Y:$Y,[2]unittypedata!$D:$D, $T34)</f>
+        <f>SUMIFS([2]unittypedata!$Z:$Z,[2]unittypedata!$D:$D, $S34)</f>
         <v>3.5</v>
       </c>
-      <c r="W34" s="8">
-        <f>SUMIFS([2]unittypedata!$Z:$Z,[2]unittypedata!$D:$D, $T34)</f>
-        <v>3.5</v>
-      </c>
-      <c r="AA34" s="37" t="s">
+      <c r="Y34" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="AB34" t="s">
-        <v>108</v>
-      </c>
-      <c r="AC34">
+      <c r="Z34" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA34">
         <v>4.4799999999999996E-3</v>
       </c>
-      <c r="AD34">
+      <c r="AB34">
         <v>0.95299999999999996</v>
       </c>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="C35" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -6309,66 +6504,74 @@
         <v>1361</v>
       </c>
       <c r="F35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1.77</v>
       </c>
       <c r="G35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>3.88</v>
       </c>
       <c r="H35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>3.88</v>
       </c>
-      <c r="I35" s="40" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J35" s="40" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K35" s="39" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="T35" t="s">
-        <v>106</v>
+      <c r="I35" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="J35" s="32" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="K35" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L35" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M35" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="S35" t="s">
+        <v>53</v>
+      </c>
+      <c r="T35" s="8">
+        <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$D:$D, $S35)</f>
+        <v>1.8</v>
       </c>
       <c r="U35" s="8">
-        <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$D:$D, $T35)</f>
-        <v>1.8</v>
+        <f>SUMIFS([2]unittypedata!$Y:$Y,[2]unittypedata!$D:$D, $S35)</f>
+        <v>3.1</v>
       </c>
       <c r="V35" s="8">
-        <f>SUMIFS([2]unittypedata!$Y:$Y,[2]unittypedata!$D:$D, $T35)</f>
+        <f>SUMIFS([2]unittypedata!$Z:$Z,[2]unittypedata!$D:$D, $S35)</f>
         <v>3.1</v>
       </c>
-      <c r="W35" s="8">
-        <f>SUMIFS([2]unittypedata!$Z:$Z,[2]unittypedata!$D:$D, $T35)</f>
-        <v>3.1</v>
-      </c>
-      <c r="AA35" s="37" t="s">
+      <c r="Y35" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="AB35" t="s">
-        <v>102</v>
-      </c>
-      <c r="AC35">
+      <c r="Z35" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA35">
         <v>3.7100000000000002E-3</v>
       </c>
-      <c r="AD35">
+      <c r="AB35">
         <v>0.82799999999999996</v>
       </c>
     </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>4</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="C36" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -6377,66 +6580,74 @@
         <v>2424</v>
       </c>
       <c r="F36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1.47</v>
       </c>
       <c r="G36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>3.21</v>
       </c>
       <c r="H36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>3.21</v>
       </c>
-      <c r="I36" s="40" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J36" s="40" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K36" s="39" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="T36" t="s">
-        <v>107</v>
+      <c r="I36" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="J36" s="32" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="K36" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L36" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M36" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="S36" t="s">
+        <v>54</v>
+      </c>
+      <c r="T36" s="8">
+        <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$D:$D, $S36)</f>
+        <v>1.4</v>
       </c>
       <c r="U36" s="8">
-        <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$D:$D, $T36)</f>
-        <v>1.4</v>
+        <f>SUMIFS([2]unittypedata!$Y:$Y,[2]unittypedata!$D:$D, $S36)</f>
+        <v>3</v>
       </c>
       <c r="V36" s="8">
-        <f>SUMIFS([2]unittypedata!$Y:$Y,[2]unittypedata!$D:$D, $T36)</f>
+        <f>SUMIFS([2]unittypedata!$Z:$Z,[2]unittypedata!$D:$D, $S36)</f>
         <v>3</v>
       </c>
-      <c r="W36" s="8">
-        <f>SUMIFS([2]unittypedata!$Z:$Z,[2]unittypedata!$D:$D, $T36)</f>
-        <v>3</v>
-      </c>
-      <c r="AA36" s="37" t="s">
+      <c r="Y36" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="AB36" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC36">
+      <c r="Z36" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA36">
         <v>7.5399999999999998E-3</v>
       </c>
-      <c r="AD36">
+      <c r="AB36">
         <v>0.59499999999999997</v>
       </c>
     </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="C37" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -6445,51 +6656,59 @@
         <v>1850</v>
       </c>
       <c r="F37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1.69</v>
       </c>
       <c r="G37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>3.69</v>
       </c>
       <c r="H37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>3.69</v>
       </c>
-      <c r="I37" s="40" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J37" s="40" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K37" s="39" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AA37" s="37" t="s">
+      <c r="I37" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="J37" s="32" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="K37" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L37" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M37" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="Y37" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="AB37" t="s">
-        <v>108</v>
-      </c>
-      <c r="AC37">
+      <c r="Z37" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA37">
         <v>1.108E-2</v>
       </c>
-      <c r="AD37">
+      <c r="AB37">
         <v>0.90500000000000003</v>
       </c>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="C38" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -6498,104 +6717,120 @@
         <v>84</v>
       </c>
       <c r="F38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.1</v>
       </c>
       <c r="G38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>4.59</v>
       </c>
       <c r="H38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>4.59</v>
       </c>
-      <c r="I38" s="40" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J38" s="40" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K38" s="39" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AA38" s="37" t="s">
+      <c r="I38" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="J38" s="32" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="K38" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L38" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M38" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="Y38" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="AB38" t="s">
-        <v>110</v>
-      </c>
-      <c r="AC38">
+      <c r="Z38" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA38">
         <v>1.108E-2</v>
       </c>
-      <c r="AD38">
+      <c r="AB38">
         <v>0.90500000000000003</v>
       </c>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="C39" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D39">
         <v>1</v>
       </c>
       <c r="F39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.12</v>
       </c>
       <c r="G39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>4.6399999999999997</v>
       </c>
       <c r="H39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>4.6399999999999997</v>
       </c>
-      <c r="I39" s="40" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J39" s="40" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K39" s="39" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="M39" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA39" s="37" t="s">
+      <c r="I39" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="J39" s="32" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="K39" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L39" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M39" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="O39" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y39" s="29" t="s">
         <v>14</v>
       </c>
+      <c r="Z39" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA39">
+        <v>5.1399999999999996E-3</v>
+      </c>
       <c r="AB39" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC39">
-        <v>5.1399999999999996E-3</v>
-      </c>
-      <c r="AD39" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="C40" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -6604,51 +6839,59 @@
         <v>1030</v>
       </c>
       <c r="F40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.0699999999999998</v>
       </c>
       <c r="G40">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>4.54</v>
       </c>
       <c r="H40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>4.54</v>
       </c>
-      <c r="I40" s="40" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J40" s="40" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K40" s="39" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AA40" s="37" t="s">
+      <c r="I40" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="J40" s="32" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="K40" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L40" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M40" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="Y40" s="29" t="s">
         <v>15</v>
       </c>
+      <c r="Z40" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA40">
+        <v>5.5599999999999998E-3</v>
+      </c>
       <c r="AB40" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC40">
-        <v>5.5599999999999998E-3</v>
-      </c>
-      <c r="AD40" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="C41" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -6657,104 +6900,120 @@
         <v>172</v>
       </c>
       <c r="F41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="G41">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>2.42</v>
       </c>
       <c r="H41">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>2.42</v>
       </c>
-      <c r="I41" s="40" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J41" s="40" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K41" s="39" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AA41" s="37" t="s">
+      <c r="I41" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="J41" s="32" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="K41" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L41" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M41" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="Y41" s="29" t="s">
         <v>16</v>
       </c>
+      <c r="Z41" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA41">
+        <v>6.4799999999999996E-3</v>
+      </c>
       <c r="AB41" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC41">
-        <v>6.4799999999999996E-3</v>
-      </c>
-      <c r="AD41" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="C42" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D42">
         <v>1</v>
       </c>
       <c r="F42">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.0299999999999998</v>
       </c>
       <c r="G42">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>3.5</v>
       </c>
       <c r="H42">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>3.5</v>
       </c>
-      <c r="I42" s="40" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J42" s="40" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K42" s="39" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="M42" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA42" s="37" t="s">
+      <c r="I42" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="J42" s="32" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="K42" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L42" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M42" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="O42" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y42" s="29" t="s">
         <v>17</v>
       </c>
+      <c r="Z42" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA42">
+        <v>8.9899999999999997E-3</v>
+      </c>
       <c r="AB42" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC42">
-        <v>8.9899999999999997E-3</v>
-      </c>
-      <c r="AD42" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="C43" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -6763,39 +7022,47 @@
         <v>1308</v>
       </c>
       <c r="F43">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.02</v>
       </c>
       <c r="G43">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>3.48</v>
       </c>
       <c r="H43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>3.48</v>
       </c>
-      <c r="I43" s="40">
-        <f t="shared" si="3"/>
+      <c r="I43" s="32">
+        <f t="shared" si="11"/>
         <v>1.3140000000000001E-2</v>
       </c>
-      <c r="J43" s="40">
-        <f t="shared" si="4"/>
+      <c r="J43" s="32">
+        <f t="shared" si="6"/>
         <v>1.3140000000000001E-2</v>
       </c>
-      <c r="K43" s="39">
-        <f t="shared" si="5"/>
+      <c r="K43" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L43" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M43" s="31">
+        <f t="shared" si="13"/>
         <v>0.84899999999999998</v>
       </c>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="C44" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -6804,39 +7071,47 @@
         <v>3989</v>
       </c>
       <c r="F44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.62</v>
       </c>
       <c r="G44">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>4.51</v>
       </c>
       <c r="H44">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>4.51</v>
       </c>
-      <c r="I44" s="40">
-        <f t="shared" si="3"/>
+      <c r="I44" s="32">
+        <f t="shared" si="11"/>
         <v>5.6600000000000001E-3</v>
       </c>
-      <c r="J44" s="40">
-        <f t="shared" si="4"/>
+      <c r="J44" s="32">
+        <f t="shared" si="6"/>
         <v>5.6600000000000001E-3</v>
       </c>
-      <c r="K44" s="39">
-        <f t="shared" si="5"/>
+      <c r="K44" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L44" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M44" s="31">
+        <f t="shared" si="13"/>
         <v>0.59299999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="C45" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -6845,39 +7120,47 @@
         <v>6056</v>
       </c>
       <c r="F45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1.99</v>
       </c>
       <c r="G45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>3.43</v>
       </c>
       <c r="H45">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>3.43</v>
       </c>
-      <c r="I45" s="40">
-        <f t="shared" si="3"/>
+      <c r="I45" s="32">
+        <f t="shared" si="11"/>
         <v>7.2399999999999999E-3</v>
       </c>
-      <c r="J45" s="40">
-        <f t="shared" si="4"/>
+      <c r="J45" s="32">
+        <f t="shared" si="6"/>
         <v>7.2399999999999999E-3</v>
       </c>
-      <c r="K45" s="39">
-        <f t="shared" si="5"/>
+      <c r="K45" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L45" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M45" s="31">
+        <f t="shared" si="13"/>
         <v>0.84799999999999998</v>
       </c>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>4</v>
       </c>
       <c r="B46" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="C46" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -6886,39 +7169,47 @@
         <v>3330</v>
       </c>
       <c r="F46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1.65</v>
       </c>
       <c r="G46">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>2.84</v>
       </c>
       <c r="H46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>2.84</v>
       </c>
-      <c r="I46" s="40">
-        <f t="shared" si="3"/>
+      <c r="I46" s="32">
+        <f t="shared" si="11"/>
         <v>8.0999999999999996E-3</v>
       </c>
-      <c r="J46" s="40">
-        <f t="shared" si="4"/>
+      <c r="J46" s="32">
+        <f t="shared" si="6"/>
         <v>8.0999999999999996E-3</v>
       </c>
-      <c r="K46" s="39" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="K46" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L46" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M46" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="C47" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -6927,39 +7218,47 @@
         <v>1950</v>
       </c>
       <c r="F47">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1.9</v>
       </c>
       <c r="G47">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>3.27</v>
       </c>
       <c r="H47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>3.27</v>
       </c>
-      <c r="I47" s="40">
-        <f t="shared" si="3"/>
+      <c r="I47" s="32">
+        <f t="shared" si="11"/>
         <v>9.3799999999999994E-3</v>
       </c>
-      <c r="J47" s="40">
-        <f t="shared" si="4"/>
+      <c r="J47" s="32">
+        <f t="shared" si="6"/>
         <v>9.3799999999999994E-3</v>
       </c>
-      <c r="K47" s="39">
-        <f t="shared" si="5"/>
+      <c r="K47" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L47" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M47" s="31">
+        <f t="shared" si="13"/>
         <v>0.89300000000000002</v>
       </c>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>7</v>
       </c>
       <c r="B48" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="C48" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -6968,39 +7267,47 @@
         <v>900</v>
       </c>
       <c r="F48">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1.38</v>
       </c>
       <c r="G48">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>2.38</v>
       </c>
       <c r="H48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>2.38</v>
       </c>
-      <c r="I48" s="40">
-        <f t="shared" si="3"/>
+      <c r="I48" s="32">
+        <f t="shared" si="11"/>
         <v>1.268E-2</v>
       </c>
-      <c r="J48" s="40">
-        <f t="shared" si="4"/>
+      <c r="J48" s="32">
+        <f t="shared" si="6"/>
         <v>1.268E-2</v>
       </c>
-      <c r="K48" s="39">
-        <f t="shared" si="5"/>
+      <c r="K48" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L48" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M48" s="31">
+        <f t="shared" si="13"/>
         <v>0.99399999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>13</v>
       </c>
       <c r="B49" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="C49" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -7009,39 +7316,47 @@
         <v>1323</v>
       </c>
       <c r="F49">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1.24</v>
       </c>
       <c r="G49">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>2.14</v>
       </c>
       <c r="H49">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>2.14</v>
       </c>
-      <c r="I49" s="40">
-        <f t="shared" si="3"/>
+      <c r="I49" s="32">
+        <f t="shared" si="11"/>
         <v>1.108E-2</v>
       </c>
-      <c r="J49" s="40">
-        <f t="shared" si="4"/>
+      <c r="J49" s="32">
+        <f t="shared" si="6"/>
         <v>1.108E-2</v>
       </c>
-      <c r="K49" s="39">
-        <f t="shared" si="5"/>
+      <c r="K49" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L49" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M49" s="31">
+        <f t="shared" si="13"/>
         <v>0.90500000000000003</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>18</v>
       </c>
       <c r="B50" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="C50" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -7050,80 +7365,96 @@
         <v>2744</v>
       </c>
       <c r="F50">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.1</v>
       </c>
       <c r="G50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>3.61</v>
       </c>
       <c r="H50">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>3.61</v>
       </c>
-      <c r="I50" s="40" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J50" s="40" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K50" s="39" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I50" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="J50" s="32" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="K50" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L50" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M50" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="C51" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D51">
         <v>1</v>
       </c>
       <c r="F51">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1.58</v>
       </c>
       <c r="G51">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>3.38</v>
       </c>
       <c r="H51">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>3.38</v>
       </c>
-      <c r="I51" s="40" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J51" s="40" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K51" s="39" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="M51" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I51" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="J51" s="32" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="K51" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L51" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M51" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="O51" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>1</v>
       </c>
       <c r="B52" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="C52" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -7132,39 +7463,47 @@
         <v>1150</v>
       </c>
       <c r="F52">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1.57</v>
       </c>
       <c r="G52">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>3.36</v>
       </c>
       <c r="H52">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>3.36</v>
       </c>
-      <c r="I52" s="40" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J52" s="40" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K52" s="39" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I52" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="J52" s="32" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="K52" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L52" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M52" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>2</v>
       </c>
       <c r="B53" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="C53" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -7173,39 +7512,47 @@
         <v>3938</v>
       </c>
       <c r="F53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>2.04</v>
       </c>
       <c r="G53">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>4.37</v>
       </c>
       <c r="H53">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>4.37</v>
       </c>
-      <c r="I53" s="40" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J53" s="40" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K53" s="39" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I53" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="J53" s="32" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="K53" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L53" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M53" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>3</v>
       </c>
       <c r="B54" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -7214,39 +7561,47 @@
         <v>6068</v>
       </c>
       <c r="F54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1.55</v>
       </c>
       <c r="G54">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>3.32</v>
       </c>
       <c r="H54">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>3.32</v>
       </c>
-      <c r="I54" s="40" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J54" s="40" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K54" s="39" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I54" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="J54" s="32" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="K54" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L54" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M54" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>4</v>
       </c>
       <c r="B55" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="C55" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -7255,39 +7610,47 @@
         <v>3142</v>
       </c>
       <c r="F55">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1.28</v>
       </c>
       <c r="G55">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>2.75</v>
       </c>
       <c r="H55">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>2.75</v>
       </c>
-      <c r="I55" s="40" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J55" s="40" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K55" s="39" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I55" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="J55" s="32" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="K55" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L55" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M55" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>6</v>
       </c>
       <c r="B56" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="C56" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -7296,39 +7659,47 @@
         <v>1950</v>
       </c>
       <c r="F56">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1.48</v>
       </c>
       <c r="G56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>3.16</v>
       </c>
       <c r="H56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>3.16</v>
       </c>
-      <c r="I56" s="40" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J56" s="40" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K56" s="39" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I56" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="J56" s="32" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="K56" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L56" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M56" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>7</v>
       </c>
       <c r="B57" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="C57" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -7337,39 +7708,47 @@
         <v>900</v>
       </c>
       <c r="F57">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1.07</v>
       </c>
       <c r="G57">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>2.2999999999999998</v>
       </c>
       <c r="H57">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>2.2999999999999998</v>
       </c>
-      <c r="I57" s="40" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J57" s="40" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K57" s="39" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I57" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="J57" s="32" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="K57" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L57" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M57" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>13</v>
       </c>
       <c r="B58" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="C58" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -7378,39 +7757,47 @@
         <v>1486</v>
       </c>
       <c r="F58">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>0.97</v>
       </c>
       <c r="G58">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>2.0699999999999998</v>
       </c>
       <c r="H58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>2.0699999999999998</v>
       </c>
-      <c r="I58" s="40" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J58" s="40" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K58" s="39" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I58" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="J58" s="32" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="K58" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L58" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M58" s="31" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>18</v>
       </c>
       <c r="B59" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="C59" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -7419,1834 +7806,40 @@
         <v>2744</v>
       </c>
       <c r="F59">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1.63</v>
       </c>
       <c r="G59">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>3.5</v>
       </c>
       <c r="H59">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>3.5</v>
       </c>
-      <c r="I59" s="40" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J59" s="40" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K59" s="39" t="str">
-        <f t="shared" si="5"/>
+      <c r="I59" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="J59" s="32" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="K59" s="33" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L59" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M59" s="31" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E70372B-D848-4D41-858E-20930D6B3715}">
-  <sheetPr>
-    <tabColor theme="7" tint="0.59999389629810485"/>
-  </sheetPr>
-  <dimension ref="A1:S58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="15.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.140625" style="6"/>
-    <col min="4" max="4" width="28.42578125" customWidth="1"/>
-    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.7109375" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="D1" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="E1" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="F1" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="G1" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="H1" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="I1" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="J1" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" t="s">
-        <v>100</v>
-      </c>
-      <c r="N1" t="s">
-        <v>100</v>
-      </c>
-      <c r="O1" t="s">
-        <v>100</v>
-      </c>
-      <c r="P1" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>100</v>
-      </c>
-      <c r="R1" t="s">
-        <v>100</v>
-      </c>
-      <c r="S1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="26">
-        <v>1</v>
-      </c>
-      <c r="C2" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I2" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="J2" s="24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="26">
-        <v>1</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="J3" s="24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="26">
-        <v>1</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="24">
-        <v>324</v>
-      </c>
-      <c r="N4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="26">
-        <v>1</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="J5" s="24">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="26">
-        <v>1</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="H6" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I6" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="J6" s="24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="26">
-        <v>1</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H7" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I7" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="J7" s="24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="26">
-        <v>1</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I8" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" s="24">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="26">
-        <v>1</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I9" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="J9" s="24">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="26">
-        <v>1</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="H10" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I10" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="J10" s="24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="26">
-        <v>1</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I11" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="J11" s="24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" s="26">
-        <v>1</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F12" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I12" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="J12" s="24">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="26">
-        <v>1</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H13" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I13" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="J13" s="24">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="26">
-        <v>1</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="G14" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="H14" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I14" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="J14" s="24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="26">
-        <v>1</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F15" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G15" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H15" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I15" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="J15" s="24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="26">
-        <v>1</v>
-      </c>
-      <c r="C16" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I16" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="J16" s="24">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="26">
-        <v>1</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H17" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I17" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="J17" s="24">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="26">
-        <v>1</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="E18" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="F18" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="G18" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="H18" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I18" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="J18" s="24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="26">
-        <v>1</v>
-      </c>
-      <c r="C19" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="E19" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F19" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G19" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H19" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I19" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="J19" s="24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="26">
-        <v>1</v>
-      </c>
-      <c r="C20" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F20" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G20" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H20" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I20" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="J20" s="24">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="26">
-        <v>1</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F21" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G21" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H21" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I21" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="J21" s="24">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="26">
-        <v>1</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="E22" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="F22" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="G22" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="H22" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I22" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="J22" s="24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="26">
-        <v>1</v>
-      </c>
-      <c r="C23" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="E23" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F23" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G23" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H23" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I23" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="J23" s="24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="26">
-        <v>1</v>
-      </c>
-      <c r="C24" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="E24" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F24" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G24" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H24" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I24" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="J24" s="24">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="26">
-        <v>1</v>
-      </c>
-      <c r="C25" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="D25" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F25" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G25" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H25" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I25" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="J25" s="24">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B26" s="26">
-        <v>1</v>
-      </c>
-      <c r="C26" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="E26" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="F26" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="G26" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="H26" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I26" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="J26" s="24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="26">
-        <v>1</v>
-      </c>
-      <c r="C27" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F27" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G27" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H27" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I27" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="J27" s="24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="26">
-        <v>1</v>
-      </c>
-      <c r="C28" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="E28" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F28" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G28" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H28" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I28" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="J28" s="24">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="26">
-        <v>1</v>
-      </c>
-      <c r="C29" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F29" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G29" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H29" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I29" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="J29" s="24">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="26">
-        <v>1</v>
-      </c>
-      <c r="C30" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="E30" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="F30" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="G30" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="H30" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I30" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="J30" s="24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" s="26">
-        <v>1</v>
-      </c>
-      <c r="C31" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D31" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F31" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G31" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H31" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I31" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="J31" s="24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B32" s="26">
-        <v>1</v>
-      </c>
-      <c r="C32" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F32" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G32" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H32" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I32" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="J32" s="24">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B33" s="26">
-        <v>1</v>
-      </c>
-      <c r="C33" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="E33" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F33" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G33" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H33" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I33" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="J33" s="24">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34" s="26">
-        <v>1</v>
-      </c>
-      <c r="C34" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="D34" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="E34" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="F34" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="G34" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="H34" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I34" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="J34" s="24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35" s="26">
-        <v>1</v>
-      </c>
-      <c r="C35" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="D35" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="E35" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F35" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G35" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H35" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I35" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="J35" s="24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36" s="26">
-        <v>1</v>
-      </c>
-      <c r="C36" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="D36" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="E36" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F36" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G36" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H36" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I36" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="J36" s="24">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37" s="26">
-        <v>1</v>
-      </c>
-      <c r="C37" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="D37" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="E37" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F37" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G37" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H37" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I37" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="J37" s="24">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="26">
-        <v>1</v>
-      </c>
-      <c r="C38" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="D38" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="E38" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="F38" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="G38" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="H38" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I38" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="J38" s="24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B39" s="26">
-        <v>1</v>
-      </c>
-      <c r="C39" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="D39" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="E39" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F39" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G39" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H39" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I39" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="J39" s="24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B40" s="26">
-        <v>1</v>
-      </c>
-      <c r="C40" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="D40" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="E40" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F40" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G40" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H40" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I40" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="J40" s="24">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B41" s="26">
-        <v>1</v>
-      </c>
-      <c r="C41" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="D41" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="E41" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F41" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G41" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H41" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I41" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="J41" s="24">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B42" s="26">
-        <v>1</v>
-      </c>
-      <c r="C42" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="D42" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="E42" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="F42" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="G42" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="H42" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I42" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="J42" s="24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B43" s="26">
-        <v>1</v>
-      </c>
-      <c r="C43" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="D43" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="E43" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F43" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G43" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H43" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I43" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="J43" s="24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B44" s="26">
-        <v>1</v>
-      </c>
-      <c r="C44" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="D44" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="E44" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F44" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G44" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H44" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I44" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="J44" s="24">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B45" s="26">
-        <v>1</v>
-      </c>
-      <c r="C45" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="D45" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="E45" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F45" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G45" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H45" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I45" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="J45" s="24">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B46" s="26">
-        <v>1</v>
-      </c>
-      <c r="C46" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="D46" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="E46" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="F46" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="G46" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="H46" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I46" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="J46" s="24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B47" s="26">
-        <v>1</v>
-      </c>
-      <c r="C47" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="D47" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="E47" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F47" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G47" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H47" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I47" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="J47" s="24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B48" s="26">
-        <v>1</v>
-      </c>
-      <c r="C48" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="D48" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="E48" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F48" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G48" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H48" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I48" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="J48" s="24">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B49" s="26">
-        <v>1</v>
-      </c>
-      <c r="C49" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="D49" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="E49" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F49" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G49" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H49" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I49" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="J49" s="24">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B50" s="26">
-        <v>1</v>
-      </c>
-      <c r="C50" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="D50" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="E50" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="F50" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="G50" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="H50" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I50" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="J50" s="24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B51" s="26">
-        <v>1</v>
-      </c>
-      <c r="C51" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="D51" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="E51" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F51" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G51" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H51" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I51" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="J51" s="24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B52" s="26">
-        <v>1</v>
-      </c>
-      <c r="C52" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="D52" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="E52" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F52" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G52" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H52" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I52" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="J52" s="24">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B53" s="26">
-        <v>1</v>
-      </c>
-      <c r="C53" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="D53" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="E53" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F53" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G53" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="H53" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I53" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="J53" s="24">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="26"/>
-      <c r="B54" s="26"/>
-      <c r="C54" s="26"/>
-      <c r="D54" s="22"/>
-      <c r="E54" s="23"/>
-      <c r="F54" s="22"/>
-      <c r="G54" s="22"/>
-      <c r="H54" s="22"/>
-      <c r="I54" s="23"/>
-      <c r="J54" s="24"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="26"/>
-      <c r="B55" s="26"/>
-      <c r="C55" s="26"/>
-      <c r="D55" s="22"/>
-      <c r="E55" s="23"/>
-      <c r="F55" s="22"/>
-      <c r="G55" s="22"/>
-      <c r="H55" s="22"/>
-      <c r="I55" s="23"/>
-      <c r="J55" s="24"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="26"/>
-      <c r="B56" s="26"/>
-      <c r="C56" s="26"/>
-      <c r="D56" s="22"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="22"/>
-      <c r="G56" s="22"/>
-      <c r="H56" s="22"/>
-      <c r="I56" s="23"/>
-      <c r="J56" s="24"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="26"/>
-      <c r="B57" s="26"/>
-      <c r="C57" s="26"/>
-      <c r="D57" s="22"/>
-      <c r="E57" s="23"/>
-      <c r="F57" s="22"/>
-      <c r="G57" s="22"/>
-      <c r="H57" s="22"/>
-      <c r="I57" s="23"/>
-      <c r="J57" s="24"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="26"/>
-      <c r="B58" s="26"/>
-      <c r="C58" s="26"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="23"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="22"/>
-      <c r="H58" s="22"/>
-      <c r="I58" s="23"/>
-      <c r="J58" s="24"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src_files/data_files/hydropower-compilation.xlsx
+++ b/src_files/data_files/hydropower-compilation.xlsx
@@ -2163,12 +2163,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4E105637-66C0-4B67-968B-A8C9BC84D774}" name="Table2" displayName="Table2" ref="A1:K41" totalsRowShown="0" headerRowDxfId="10">
-  <autoFilter ref="A1:K41" xr:uid="{4E105637-66C0-4B67-968B-A8C9BC84D774}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4E105637-66C0-4B67-968B-A8C9BC84D774}" name="Table2" displayName="Table2" ref="A1:L41" totalsRowShown="0" headerRowDxfId="10">
+  <autoFilter ref="A1:L41" xr:uid="{4E105637-66C0-4B67-968B-A8C9BC84D774}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I6">
     <sortCondition ref="B1:B6"/>
   </sortState>
-  <tableColumns count="11">
+  <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{DD34CF7B-7E89-4129-B187-64EA9DBE9AB5}" name="Country" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{9F2751A6-04EC-4ED2-AB42-B8EA5F26204C}" name="Grid"/>
     <tableColumn id="4" xr3:uid="{9BB2F988-4BF3-43BE-825B-61D7ED214C20}" name="Scenario" dataDxfId="8"/>
@@ -2180,6 +2180,7 @@
     <tableColumn id="9" xr3:uid="{84FDFFC6-278E-4FC6-9D54-9736721D6070}" name="maxSpill" dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{4277BD29-04AE-4F26-8CE8-222C6FFCB3F8}" name="Method" dataDxfId="1"/>
     <tableColumn id="11" xr3:uid="{B3AB9226-4E6B-449D-A1AB-E1E4E89232A7}" name="Note" dataDxfId="0"/>
+    <tableColumn id="12" xr3:uid="{F68C3CE4-3C56-4F8E-8DD3-83A348B09906}" name="relative"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2500,6 +2501,11 @@
       <c r="K1" s="23" t="s">
         <v>35</v>
       </c>
+      <c r="L1" s="11" t="inlineStr">
+        <is>
+          <t>relative</t>
+        </is>
+      </c>
       <c r="O1" t="s">
         <v>47</v>
       </c>
@@ -2959,6 +2965,9 @@
       </c>
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
+      <c r="L13" s="12">
+        <v>0.9</v>
+      </c>
       <c r="P13" s="28" t="s">
         <v>8</v>
       </c>
@@ -2999,6 +3008,9 @@
       </c>
       <c r="J14" s="12"/>
       <c r="K14" s="12"/>
+      <c r="L14" s="12">
+        <v>0.68</v>
+      </c>
       <c r="P14" s="28" t="s">
         <v>13</v>
       </c>
@@ -3039,6 +3051,9 @@
       </c>
       <c r="J15" s="12"/>
       <c r="K15" s="12"/>
+      <c r="L15" s="12">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
@@ -3068,8 +3083,11 @@
       </c>
       <c r="J16" s="12"/>
       <c r="K16" s="12"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L16" s="12">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>5</v>
       </c>
@@ -3097,8 +3115,11 @@
       </c>
       <c r="J17" s="12"/>
       <c r="K17" s="12"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L17" s="12">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>6</v>
       </c>
@@ -3126,8 +3147,11 @@
       </c>
       <c r="J18" s="12"/>
       <c r="K18" s="12"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L18" s="12">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>13</v>
       </c>
@@ -3155,8 +3179,11 @@
       </c>
       <c r="J19" s="12"/>
       <c r="K19" s="12"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L19" s="12">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>14</v>
       </c>
@@ -3184,8 +3211,11 @@
       </c>
       <c r="J20" s="12"/>
       <c r="K20" s="12"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L20" s="12">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>15</v>
       </c>
@@ -3213,8 +3243,11 @@
       </c>
       <c r="J21" s="12"/>
       <c r="K21" s="24"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L21" s="12">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>16</v>
       </c>
@@ -3242,8 +3275,11 @@
       </c>
       <c r="J22" s="12"/>
       <c r="K22" s="12"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L22" s="12">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>17</v>
       </c>
@@ -3271,8 +3307,11 @@
       </c>
       <c r="J23" s="12"/>
       <c r="K23" s="12"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L23" s="12">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>0</v>
       </c>
@@ -3300,6 +3339,9 @@
       </c>
       <c r="J24" s="12"/>
       <c r="K24" s="12"/>
+      <c r="L24" s="12">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
@@ -3325,7 +3367,7 @@
       </c>
       <c r="K25" s="12"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
         <v>3</v>
       </c>
@@ -3353,8 +3395,11 @@
       </c>
       <c r="J26" s="12"/>
       <c r="K26" s="12"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L26" s="12">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>4</v>
       </c>
@@ -3382,8 +3427,11 @@
       </c>
       <c r="J27" s="12"/>
       <c r="K27" s="12"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L27" s="12">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>6</v>
       </c>
@@ -3411,8 +3459,11 @@
       </c>
       <c r="J28" s="12"/>
       <c r="K28" s="12"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L28" s="12">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
         <v>10</v>
       </c>
@@ -3440,8 +3491,11 @@
       </c>
       <c r="J29" s="12"/>
       <c r="K29" s="12"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L29" s="12">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
         <v>11</v>
       </c>
@@ -3469,8 +3523,11 @@
       </c>
       <c r="J30" s="12"/>
       <c r="K30" s="24"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L30" s="12">
+        <v>0.56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
         <v>12</v>
       </c>
@@ -3498,8 +3555,11 @@
       </c>
       <c r="J31" s="12"/>
       <c r="K31" s="24"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L31" s="12">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
         <v>13</v>
       </c>
@@ -3527,6 +3587,9 @@
       </c>
       <c r="J32" s="12"/>
       <c r="K32" s="12"/>
+      <c r="L32" s="12">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">

--- a/src_files/data_files/hydropower-compilation.xlsx
+++ b/src_files/data_files/hydropower-compilation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BB\bb-dev\north_european_model\src_files\data_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E8FC15-7493-4D49-B15B-252B3F97727A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45AE226E-B748-4DD7-9F41-D8F68740159E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1080" windowWidth="21600" windowHeight="12585" tabRatio="747" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="747" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nodedata" sheetId="13" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="83">
   <si>
     <t>AT00</t>
   </si>
@@ -369,6 +369,9 @@
   </si>
   <si>
     <t>minGenPenalty</t>
+  </si>
+  <si>
+    <t>relative</t>
   </si>
 </sst>
 </file>
@@ -483,7 +486,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -529,6 +532,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,7 +592,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -660,6 +669,7 @@
     <xf numFmtId="1" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1076,20 +1086,20 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2501,10 +2511,8 @@
       <c r="K1" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="L1" s="11" t="inlineStr">
-        <is>
-          <t>relative</t>
-        </is>
+      <c r="L1" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="O1" t="s">
         <v>47</v>
@@ -3343,7 +3351,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>2</v>
       </c>
@@ -3524,7 +3532,7 @@
       <c r="J30" s="12"/>
       <c r="K30" s="24"/>
       <c r="L30" s="12">
-        <v>0.56</v>
+        <v>0.56000000000000005</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -3999,11 +4007,11 @@
       </c>
       <c r="I2" s="32">
         <f t="shared" ref="I2:I33" si="3">IF(ROUND(SUMIFS($AA$8:$AA$42, $Y$8:$Y$42,$A2,    $Z$8:$Z$42,$B2), 5)&gt;0, ROUND(SUMIFS($AA$8:$AA$42, $Y$8:$Y$42,$A2,    $Z$8:$Z$42,$B2), 5), "")</f>
-        <v>2.31E-3</v>
+        <v>3.31E-3</v>
       </c>
       <c r="J2" s="32">
         <f>I2</f>
-        <v>2.31E-3</v>
+        <v>3.31E-3</v>
       </c>
       <c r="K2" s="33">
         <f t="shared" ref="K2:K33" si="4">IF(SUMIFS($AF$7:$AF$19,    $AD$7:$AD$19,$A2,     $AE$7:$AE$19,$B2)&gt;0, SUMIFS($AF$7:$AF$19,    $AD$7:$AD$19,$A2,     $AE$7:$AE$19,$B2), "")</f>
@@ -4149,11 +4157,11 @@
       </c>
       <c r="I5" s="32">
         <f t="shared" si="3"/>
-        <v>2.9499999999999999E-3</v>
+        <v>3.9500000000000004E-3</v>
       </c>
       <c r="J5" s="32">
         <f t="shared" si="6"/>
-        <v>2.9499999999999999E-3</v>
+        <v>3.9500000000000004E-3</v>
       </c>
       <c r="K5" s="33">
         <f t="shared" si="4"/>
@@ -4400,8 +4408,9 @@
       <c r="Z8" t="s">
         <v>49</v>
       </c>
-      <c r="AA8">
-        <v>2.31E-3</v>
+      <c r="AA8" s="34">
+        <f>0.00231+0.001</f>
+        <v>3.31E-3</v>
       </c>
       <c r="AB8">
         <v>0.92500000000000004</v>
@@ -5112,8 +5121,9 @@
       <c r="Z16" t="s">
         <v>49</v>
       </c>
-      <c r="AA16">
-        <v>2.9499999999999999E-3</v>
+      <c r="AA16" s="34">
+        <f>0.00295+0.001</f>
+        <v>3.9500000000000004E-3</v>
       </c>
       <c r="AB16">
         <v>0.61399999999999999</v>
